--- a/eval/elifeBaseLlmEval.xlsx
+++ b/eval/elifeBaseLlmEval.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G243"/>
+  <dimension ref="A1:I243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,16 @@
           <t>CLI</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>BERTScore</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>SummaC</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,10 +482,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.41509434</v>
+        <v>0.4150943396226415</v>
       </c>
       <c r="C2" t="n">
-        <v>0.128787879</v>
+        <v>0.1287878787878788</v>
       </c>
       <c r="D2" t="n">
         <v>0.4</v>
@@ -489,6 +499,12 @@
       <c r="G2" t="n">
         <v>14.33</v>
       </c>
+      <c r="H2" t="n">
+        <v>0.8465633988380432</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2789794504642487</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -497,13 +513,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.449579832</v>
+        <v>0.4495798319327731</v>
       </c>
       <c r="C3" t="n">
-        <v>0.084388186</v>
+        <v>0.08438818565400844</v>
       </c>
       <c r="D3" t="n">
-        <v>0.420168067</v>
+        <v>0.4201680672268908</v>
       </c>
       <c r="E3" t="n">
         <v>15.1</v>
@@ -514,6 +530,12 @@
       <c r="G3" t="n">
         <v>14.97</v>
       </c>
+      <c r="H3" t="n">
+        <v>0.8657573461532593</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2310424894094467</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -522,13 +544,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.402618658</v>
+        <v>0.4026186579378069</v>
       </c>
       <c r="C4" t="n">
-        <v>0.147783251</v>
+        <v>0.1477832512315271</v>
       </c>
       <c r="D4" t="n">
-        <v>0.379705401</v>
+        <v>0.3797054009819967</v>
       </c>
       <c r="E4" t="n">
         <v>9.300000000000001</v>
@@ -539,6 +561,12 @@
       <c r="G4" t="n">
         <v>11.89</v>
       </c>
+      <c r="H4" t="n">
+        <v>0.836020827293396</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3187246918678284</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -547,13 +575,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.334085779</v>
+        <v>0.3340857787810383</v>
       </c>
       <c r="C5" t="n">
-        <v>0.068027211</v>
+        <v>0.06802721088435373</v>
       </c>
       <c r="D5" t="n">
-        <v>0.316027088</v>
+        <v>0.3160270880361174</v>
       </c>
       <c r="E5" t="n">
         <v>13.1</v>
@@ -564,6 +592,12 @@
       <c r="G5" t="n">
         <v>12.65</v>
       </c>
+      <c r="H5" t="n">
+        <v>0.8457622528076172</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2185571789741516</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -572,13 +606,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.382417582</v>
+        <v>0.3824175824175824</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09271523199999999</v>
+        <v>0.09271523178807947</v>
       </c>
       <c r="D6" t="n">
-        <v>0.36043956</v>
+        <v>0.3604395604395605</v>
       </c>
       <c r="E6" t="n">
         <v>15.8</v>
@@ -589,6 +623,12 @@
       <c r="G6" t="n">
         <v>16.6</v>
       </c>
+      <c r="H6" t="n">
+        <v>0.8394652605056763</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2242499887943268</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -597,13 +637,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.409638554</v>
+        <v>0.4096385542168675</v>
       </c>
       <c r="C7" t="n">
-        <v>0.110535406</v>
+        <v>0.1105354058721934</v>
       </c>
       <c r="D7" t="n">
-        <v>0.39242685</v>
+        <v>0.3924268502581755</v>
       </c>
       <c r="E7" t="n">
         <v>11.8</v>
@@ -614,6 +654,12 @@
       <c r="G7" t="n">
         <v>14.39</v>
       </c>
+      <c r="H7" t="n">
+        <v>0.8453882336616516</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2620471119880676</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -622,13 +668,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.381294964</v>
+        <v>0.381294964028777</v>
       </c>
       <c r="C8" t="n">
-        <v>0.090252708</v>
+        <v>0.09025270758122744</v>
       </c>
       <c r="D8" t="n">
-        <v>0.348920863</v>
+        <v>0.3489208633093525</v>
       </c>
       <c r="E8" t="n">
         <v>14.8</v>
@@ -639,6 +685,12 @@
       <c r="G8" t="n">
         <v>16.53</v>
       </c>
+      <c r="H8" t="n">
+        <v>0.840739369392395</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2319335788488388</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -647,13 +699,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.418699187</v>
+        <v>0.41869918699187</v>
       </c>
       <c r="C9" t="n">
-        <v>0.106122449</v>
+        <v>0.1061224489795918</v>
       </c>
       <c r="D9" t="n">
-        <v>0.410569106</v>
+        <v>0.4105691056910569</v>
       </c>
       <c r="E9" t="n">
         <v>10.5</v>
@@ -664,6 +716,12 @@
       <c r="G9" t="n">
         <v>10.15</v>
       </c>
+      <c r="H9" t="n">
+        <v>0.8512138724327087</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2256479859352112</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -672,13 +730,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.392014519</v>
+        <v>0.3920145190562613</v>
       </c>
       <c r="C10" t="n">
-        <v>0.102003643</v>
+        <v>0.1020036429872495</v>
       </c>
       <c r="D10" t="n">
-        <v>0.366606171</v>
+        <v>0.366606170598911</v>
       </c>
       <c r="E10" t="n">
         <v>14</v>
@@ -689,6 +747,12 @@
       <c r="G10" t="n">
         <v>13.12</v>
       </c>
+      <c r="H10" t="n">
+        <v>0.8540167212486267</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2420045286417007</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -697,13 +761,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.351239669</v>
+        <v>0.3512396694214876</v>
       </c>
       <c r="C11" t="n">
-        <v>0.053941909</v>
+        <v>0.05394190871369294</v>
       </c>
       <c r="D11" t="n">
-        <v>0.289256198</v>
+        <v>0.2892561983471075</v>
       </c>
       <c r="E11" t="n">
         <v>13.4</v>
@@ -714,6 +778,12 @@
       <c r="G11" t="n">
         <v>15.03</v>
       </c>
+      <c r="H11" t="n">
+        <v>0.8306583762168884</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2231022864580154</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -722,13 +792,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.36677116</v>
+        <v>0.3667711598746081</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09748427699999999</v>
+        <v>0.09748427672955975</v>
       </c>
       <c r="D12" t="n">
-        <v>0.34169279</v>
+        <v>0.341692789968652</v>
       </c>
       <c r="E12" t="n">
         <v>15.9</v>
@@ -739,6 +809,12 @@
       <c r="G12" t="n">
         <v>16.83</v>
       </c>
+      <c r="H12" t="n">
+        <v>0.8387457132339478</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2500491738319397</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -747,13 +823,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.350340136</v>
+        <v>0.3503401360544218</v>
       </c>
       <c r="C13" t="n">
-        <v>0.122866894</v>
+        <v>0.1228668941979522</v>
       </c>
       <c r="D13" t="n">
-        <v>0.326530612</v>
+        <v>0.3265306122448979</v>
       </c>
       <c r="E13" t="n">
         <v>10.7</v>
@@ -764,6 +840,12 @@
       <c r="G13" t="n">
         <v>13.46</v>
       </c>
+      <c r="H13" t="n">
+        <v>0.8457517027854919</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2429959625005722</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -772,13 +854,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.453222453</v>
+        <v>0.4532224532224532</v>
       </c>
       <c r="C14" t="n">
-        <v>0.091858038</v>
+        <v>0.09185803757828812</v>
       </c>
       <c r="D14" t="n">
-        <v>0.428274428</v>
+        <v>0.4282744282744283</v>
       </c>
       <c r="E14" t="n">
         <v>10.2</v>
@@ -789,6 +871,12 @@
       <c r="G14" t="n">
         <v>10.79</v>
       </c>
+      <c r="H14" t="n">
+        <v>0.8460411429405212</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2252527177333832</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -797,13 +885,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.44017094</v>
+        <v>0.4401709401709402</v>
       </c>
       <c r="C15" t="n">
-        <v>0.111587983</v>
+        <v>0.111587982832618</v>
       </c>
       <c r="D15" t="n">
-        <v>0.38034188</v>
+        <v>0.3803418803418804</v>
       </c>
       <c r="E15" t="n">
         <v>12.3</v>
@@ -814,6 +902,12 @@
       <c r="G15" t="n">
         <v>13.52</v>
       </c>
+      <c r="H15" t="n">
+        <v>0.856675922870636</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2338729947805405</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -822,13 +916,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.380038388</v>
+        <v>0.3800383877159309</v>
       </c>
       <c r="C16" t="n">
-        <v>0.073217726</v>
+        <v>0.07321772639691715</v>
       </c>
       <c r="D16" t="n">
-        <v>0.322456814</v>
+        <v>0.3224568138195777</v>
       </c>
       <c r="E16" t="n">
         <v>15.7</v>
@@ -839,6 +933,12 @@
       <c r="G16" t="n">
         <v>17.12</v>
       </c>
+      <c r="H16" t="n">
+        <v>0.8429776430130005</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2355196475982666</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -847,13 +947,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.392638037</v>
+        <v>0.3926380368098159</v>
       </c>
       <c r="C17" t="n">
-        <v>0.064615385</v>
+        <v>0.06461538461538462</v>
       </c>
       <c r="D17" t="n">
-        <v>0.365030675</v>
+        <v>0.3650306748466258</v>
       </c>
       <c r="E17" t="n">
         <v>14.5</v>
@@ -864,6 +964,12 @@
       <c r="G17" t="n">
         <v>16.01</v>
       </c>
+      <c r="H17" t="n">
+        <v>0.8288080096244812</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2316260635852814</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -872,13 +978,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.467640919</v>
+        <v>0.4676409185803758</v>
       </c>
       <c r="C18" t="n">
-        <v>0.100628931</v>
+        <v>0.1006289308176101</v>
       </c>
       <c r="D18" t="n">
-        <v>0.446764092</v>
+        <v>0.4467640918580376</v>
       </c>
       <c r="E18" t="n">
         <v>13.9</v>
@@ -889,6 +995,12 @@
       <c r="G18" t="n">
         <v>14.33</v>
       </c>
+      <c r="H18" t="n">
+        <v>0.8603586554527283</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.223340630531311</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -897,13 +1009,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.455645161</v>
+        <v>0.4556451612903225</v>
       </c>
       <c r="C19" t="n">
-        <v>0.089068826</v>
+        <v>0.08906882591093118</v>
       </c>
       <c r="D19" t="n">
-        <v>0.419354839</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="E19" t="n">
         <v>11.2</v>
@@ -914,6 +1026,12 @@
       <c r="G19" t="n">
         <v>13</v>
       </c>
+      <c r="H19" t="n">
+        <v>0.8590113520622253</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2305290549993515</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -922,13 +1040,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.405594406</v>
+        <v>0.4055944055944056</v>
       </c>
       <c r="C20" t="n">
-        <v>0.066666667</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="D20" t="n">
-        <v>0.374125874</v>
+        <v>0.3741258741258741</v>
       </c>
       <c r="E20" t="n">
         <v>15.8</v>
@@ -939,6 +1057,12 @@
       <c r="G20" t="n">
         <v>17.64</v>
       </c>
+      <c r="H20" t="n">
+        <v>0.8433234095573425</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2428673803806305</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -947,13 +1071,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.341650672</v>
+        <v>0.3416506717850288</v>
       </c>
       <c r="C21" t="n">
-        <v>0.077071291</v>
+        <v>0.07707129094412331</v>
       </c>
       <c r="D21" t="n">
-        <v>0.322456814</v>
+        <v>0.3224568138195777</v>
       </c>
       <c r="E21" t="n">
         <v>13.1</v>
@@ -964,6 +1088,12 @@
       <c r="G21" t="n">
         <v>15.26</v>
       </c>
+      <c r="H21" t="n">
+        <v>0.8396130204200745</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.24056276679039</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -972,13 +1102,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.369186047</v>
+        <v>0.3691860465116279</v>
       </c>
       <c r="C22" t="n">
-        <v>0.093294461</v>
+        <v>0.09329446064139942</v>
       </c>
       <c r="D22" t="n">
-        <v>0.354651163</v>
+        <v>0.3546511627906977</v>
       </c>
       <c r="E22" t="n">
         <v>15.5</v>
@@ -989,6 +1119,12 @@
       <c r="G22" t="n">
         <v>15.37</v>
       </c>
+      <c r="H22" t="n">
+        <v>0.828305184841156</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2543567419052124</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -997,13 +1133,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.43902439</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="C23" t="n">
-        <v>0.161764706</v>
+        <v>0.1617647058823529</v>
       </c>
       <c r="D23" t="n">
-        <v>0.409756098</v>
+        <v>0.4097560975609756</v>
       </c>
       <c r="E23" t="n">
         <v>11.9</v>
@@ -1014,6 +1150,12 @@
       <c r="G23" t="n">
         <v>12.88</v>
       </c>
+      <c r="H23" t="n">
+        <v>0.8622100949287415</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.221619039773941</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1022,13 +1164,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.405919662</v>
+        <v>0.4059196617336152</v>
       </c>
       <c r="C24" t="n">
-        <v>0.067940552</v>
+        <v>0.06794055201698514</v>
       </c>
       <c r="D24" t="n">
-        <v>0.380549683</v>
+        <v>0.3805496828752642</v>
       </c>
       <c r="E24" t="n">
         <v>12.9</v>
@@ -1039,6 +1181,12 @@
       <c r="G24" t="n">
         <v>15.03</v>
       </c>
+      <c r="H24" t="n">
+        <v>0.8446075320243835</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.239797368645668</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1047,13 +1195,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.413001912</v>
+        <v>0.4130019120458892</v>
       </c>
       <c r="C25" t="n">
-        <v>0.111324376</v>
+        <v>0.1113243761996161</v>
       </c>
       <c r="D25" t="n">
-        <v>0.370936902</v>
+        <v>0.3709369024856597</v>
       </c>
       <c r="E25" t="n">
         <v>14</v>
@@ -1064,6 +1212,12 @@
       <c r="G25" t="n">
         <v>13.46</v>
       </c>
+      <c r="H25" t="n">
+        <v>0.8366545438766479</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2325475364923477</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1072,13 +1226,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.355648536</v>
+        <v>0.3556485355648536</v>
       </c>
       <c r="C26" t="n">
-        <v>0.08823529400000001</v>
+        <v>0.08823529411764705</v>
       </c>
       <c r="D26" t="n">
-        <v>0.309623431</v>
+        <v>0.3096234309623431</v>
       </c>
       <c r="E26" t="n">
         <v>17.3</v>
@@ -1089,6 +1243,12 @@
       <c r="G26" t="n">
         <v>16.42</v>
       </c>
+      <c r="H26" t="n">
+        <v>0.837774395942688</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2442997246980667</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1100,7 +1260,7 @@
         <v>0.3712</v>
       </c>
       <c r="C27" t="n">
-        <v>0.102728732</v>
+        <v>0.1027287319422151</v>
       </c>
       <c r="D27" t="n">
         <v>0.3424</v>
@@ -1114,6 +1274,12 @@
       <c r="G27" t="n">
         <v>14.68</v>
       </c>
+      <c r="H27" t="n">
+        <v>0.843207836151123</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2479308396577835</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1122,13 +1288,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.405727924</v>
+        <v>0.405727923627685</v>
       </c>
       <c r="C28" t="n">
-        <v>0.086330935</v>
+        <v>0.08633093525179855</v>
       </c>
       <c r="D28" t="n">
-        <v>0.381861575</v>
+        <v>0.3818615751789976</v>
       </c>
       <c r="E28" t="n">
         <v>11.1</v>
@@ -1139,6 +1305,12 @@
       <c r="G28" t="n">
         <v>12.18</v>
       </c>
+      <c r="H28" t="n">
+        <v>0.8525347709655762</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2214551270008087</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1147,13 +1319,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.417218543</v>
+        <v>0.4172185430463576</v>
       </c>
       <c r="C29" t="n">
-        <v>0.059800664</v>
+        <v>0.05980066445182725</v>
       </c>
       <c r="D29" t="n">
-        <v>0.364238411</v>
+        <v>0.3642384105960265</v>
       </c>
       <c r="E29" t="n">
         <v>16.6</v>
@@ -1164,6 +1336,12 @@
       <c r="G29" t="n">
         <v>16.48</v>
       </c>
+      <c r="H29" t="n">
+        <v>0.8398507833480835</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2355972081422806</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1172,13 +1350,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.44140625</v>
+        <v>0.4414062499999999</v>
       </c>
       <c r="C30" t="n">
-        <v>0.109803922</v>
+        <v>0.1098039215686275</v>
       </c>
       <c r="D30" t="n">
-        <v>0.40234375</v>
+        <v>0.4023437500000001</v>
       </c>
       <c r="E30" t="n">
         <v>12.3</v>
@@ -1189,6 +1367,12 @@
       <c r="G30" t="n">
         <v>12.94</v>
       </c>
+      <c r="H30" t="n">
+        <v>0.845141589641571</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.2466163486242294</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1197,13 +1381,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.329268293</v>
+        <v>0.3292682926829268</v>
       </c>
       <c r="C31" t="n">
-        <v>0.073394495</v>
+        <v>0.07339449541284404</v>
       </c>
       <c r="D31" t="n">
-        <v>0.304878049</v>
+        <v>0.3048780487804879</v>
       </c>
       <c r="E31" t="n">
         <v>15.7</v>
@@ -1214,6 +1398,12 @@
       <c r="G31" t="n">
         <v>16.02</v>
       </c>
+      <c r="H31" t="n">
+        <v>0.8263953924179077</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.2412315607070923</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1222,13 +1412,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.351401869</v>
+        <v>0.3514018691588785</v>
       </c>
       <c r="C32" t="n">
-        <v>0.120075047</v>
+        <v>0.1200750469043152</v>
       </c>
       <c r="D32" t="n">
-        <v>0.336448598</v>
+        <v>0.3364485981308411</v>
       </c>
       <c r="E32" t="n">
         <v>10.1</v>
@@ -1239,6 +1429,12 @@
       <c r="G32" t="n">
         <v>12</v>
       </c>
+      <c r="H32" t="n">
+        <v>0.84720379114151</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.2257455885410309</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1247,13 +1443,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.387173397</v>
+        <v>0.3871733966745843</v>
       </c>
       <c r="C33" t="n">
-        <v>0.073809524</v>
+        <v>0.07380952380952381</v>
       </c>
       <c r="D33" t="n">
-        <v>0.356294537</v>
+        <v>0.3562945368171021</v>
       </c>
       <c r="E33" t="n">
         <v>11.5</v>
@@ -1264,6 +1460,12 @@
       <c r="G33" t="n">
         <v>11.37</v>
       </c>
+      <c r="H33" t="n">
+        <v>0.8321826457977295</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.2580804824829102</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1272,13 +1474,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.386117137</v>
+        <v>0.386117136659436</v>
       </c>
       <c r="C34" t="n">
-        <v>0.09586056599999999</v>
+        <v>0.09586056644880173</v>
       </c>
       <c r="D34" t="n">
-        <v>0.355748373</v>
+        <v>0.3557483731019523</v>
       </c>
       <c r="E34" t="n">
         <v>10.2</v>
@@ -1289,6 +1491,12 @@
       <c r="G34" t="n">
         <v>11.55</v>
       </c>
+      <c r="H34" t="n">
+        <v>0.8525648713111877</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.230742558836937</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1297,13 +1505,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.379506641</v>
+        <v>0.3795066413662239</v>
       </c>
       <c r="C35" t="n">
-        <v>0.09523809499999999</v>
+        <v>0.09523809523809525</v>
       </c>
       <c r="D35" t="n">
-        <v>0.34914611</v>
+        <v>0.349146110056926</v>
       </c>
       <c r="E35" t="n">
         <v>11.2</v>
@@ -1314,6 +1522,12 @@
       <c r="G35" t="n">
         <v>14.04</v>
       </c>
+      <c r="H35" t="n">
+        <v>0.8451489210128784</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.2409243732690811</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1322,13 +1536,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.378167641</v>
+        <v>0.378167641325536</v>
       </c>
       <c r="C36" t="n">
-        <v>0.078277886</v>
+        <v>0.07827788649706457</v>
       </c>
       <c r="D36" t="n">
-        <v>0.358674464</v>
+        <v>0.3586744639376218</v>
       </c>
       <c r="E36" t="n">
         <v>11.1</v>
@@ -1339,6 +1553,12 @@
       <c r="G36" t="n">
         <v>12.36</v>
       </c>
+      <c r="H36" t="n">
+        <v>0.8469411134719849</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2465378940105438</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1347,13 +1567,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.44486692</v>
+        <v>0.4448669201520913</v>
       </c>
       <c r="C37" t="n">
-        <v>0.103053435</v>
+        <v>0.1030534351145038</v>
       </c>
       <c r="D37" t="n">
-        <v>0.399239544</v>
+        <v>0.3992395437262358</v>
       </c>
       <c r="E37" t="n">
         <v>13.6</v>
@@ -1364,6 +1584,12 @@
       <c r="G37" t="n">
         <v>13.69</v>
       </c>
+      <c r="H37" t="n">
+        <v>0.8504480123519897</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2466840445995331</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1372,13 +1598,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.451612903</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="C38" t="n">
-        <v>0.103671706</v>
+        <v>0.1036717062634989</v>
       </c>
       <c r="D38" t="n">
-        <v>0.417204301</v>
+        <v>0.4172043010752688</v>
       </c>
       <c r="E38" t="n">
         <v>12.4</v>
@@ -1389,6 +1615,12 @@
       <c r="G38" t="n">
         <v>14.27</v>
       </c>
+      <c r="H38" t="n">
+        <v>0.8508447408676147</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2276161462068558</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1397,13 +1629,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.438162544</v>
+        <v>0.4381625441696113</v>
       </c>
       <c r="C39" t="n">
-        <v>0.106382979</v>
+        <v>0.1063829787234043</v>
       </c>
       <c r="D39" t="n">
-        <v>0.385159011</v>
+        <v>0.3851590106007068</v>
       </c>
       <c r="E39" t="n">
         <v>12.8</v>
@@ -1414,6 +1646,12 @@
       <c r="G39" t="n">
         <v>15.66</v>
       </c>
+      <c r="H39" t="n">
+        <v>0.8514916896820068</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.2365701645612717</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1422,13 +1660,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.42516269</v>
+        <v>0.4251626898047722</v>
       </c>
       <c r="C40" t="n">
-        <v>0.08278867099999999</v>
+        <v>0.08278867102396514</v>
       </c>
       <c r="D40" t="n">
-        <v>0.394793926</v>
+        <v>0.3947939262472885</v>
       </c>
       <c r="E40" t="n">
         <v>14.6</v>
@@ -1439,6 +1677,12 @@
       <c r="G40" t="n">
         <v>14.8</v>
       </c>
+      <c r="H40" t="n">
+        <v>0.836839497089386</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.2253516614437103</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1447,13 +1691,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.426373626</v>
+        <v>0.4263736263736264</v>
       </c>
       <c r="C41" t="n">
-        <v>0.101545254</v>
+        <v>0.1015452538631346</v>
       </c>
       <c r="D41" t="n">
-        <v>0.382417582</v>
+        <v>0.3824175824175824</v>
       </c>
       <c r="E41" t="n">
         <v>12</v>
@@ -1464,6 +1708,12 @@
       <c r="G41" t="n">
         <v>14.27</v>
       </c>
+      <c r="H41" t="n">
+        <v>0.8548415899276733</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.2294942587614059</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1472,13 +1722,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.479371316</v>
+        <v>0.4793713163064833</v>
       </c>
       <c r="C42" t="n">
-        <v>0.138067061</v>
+        <v>0.1380670611439842</v>
       </c>
       <c r="D42" t="n">
-        <v>0.440078585</v>
+        <v>0.4400785854616896</v>
       </c>
       <c r="E42" t="n">
         <v>11.3</v>
@@ -1489,6 +1739,12 @@
       <c r="G42" t="n">
         <v>12.59</v>
       </c>
+      <c r="H42" t="n">
+        <v>0.8498903512954712</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.2287292033433914</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1497,13 +1753,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.403162055</v>
+        <v>0.4031620553359684</v>
       </c>
       <c r="C43" t="n">
-        <v>0.087301587</v>
+        <v>0.08730158730158731</v>
       </c>
       <c r="D43" t="n">
-        <v>0.375494071</v>
+        <v>0.3754940711462451</v>
       </c>
       <c r="E43" t="n">
         <v>15.8</v>
@@ -1514,6 +1770,12 @@
       <c r="G43" t="n">
         <v>13.87</v>
       </c>
+      <c r="H43" t="n">
+        <v>0.8409797549247742</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.2212850153446198</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1522,13 +1784,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.383141762</v>
+        <v>0.3831417624521072</v>
       </c>
       <c r="C44" t="n">
-        <v>0.103846154</v>
+        <v>0.1038461538461539</v>
       </c>
       <c r="D44" t="n">
-        <v>0.352490421</v>
+        <v>0.3524904214559387</v>
       </c>
       <c r="E44" t="n">
         <v>11.8</v>
@@ -1539,6 +1801,12 @@
       <c r="G44" t="n">
         <v>13.69</v>
       </c>
+      <c r="H44" t="n">
+        <v>0.836097776889801</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.2386208921670914</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1547,13 +1815,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.323049002</v>
+        <v>0.323049001814882</v>
       </c>
       <c r="C45" t="n">
-        <v>0.06557377</v>
+        <v>0.06557377049180328</v>
       </c>
       <c r="D45" t="n">
-        <v>0.286751361</v>
+        <v>0.2867513611615245</v>
       </c>
       <c r="E45" t="n">
         <v>13.1</v>
@@ -1564,6 +1832,12 @@
       <c r="G45" t="n">
         <v>15.61</v>
       </c>
+      <c r="H45" t="n">
+        <v>0.8423702716827393</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.2368962317705154</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1572,13 +1846,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.379204893</v>
+        <v>0.3792048929663609</v>
       </c>
       <c r="C46" t="n">
-        <v>0.104294479</v>
+        <v>0.1042944785276074</v>
       </c>
       <c r="D46" t="n">
-        <v>0.333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E46" t="n">
         <v>11.6</v>
@@ -1589,6 +1863,12 @@
       <c r="G46" t="n">
         <v>13.34</v>
       </c>
+      <c r="H46" t="n">
+        <v>0.8291229605674744</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.2835615575313568</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1597,13 +1877,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.400756144</v>
+        <v>0.4007561436672968</v>
       </c>
       <c r="C47" t="n">
-        <v>0.041745731</v>
+        <v>0.04174573055028463</v>
       </c>
       <c r="D47" t="n">
-        <v>0.381852552</v>
+        <v>0.3818525519848771</v>
       </c>
       <c r="E47" t="n">
         <v>16.3</v>
@@ -1614,6 +1894,12 @@
       <c r="G47" t="n">
         <v>17</v>
       </c>
+      <c r="H47" t="n">
+        <v>0.8311726450920105</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.2558735013008118</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1622,13 +1908,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.427906977</v>
+        <v>0.427906976744186</v>
       </c>
       <c r="C48" t="n">
-        <v>0.102803738</v>
+        <v>0.102803738317757</v>
       </c>
       <c r="D48" t="n">
-        <v>0.386046512</v>
+        <v>0.386046511627907</v>
       </c>
       <c r="E48" t="n">
         <v>15</v>
@@ -1639,6 +1925,12 @@
       <c r="G48" t="n">
         <v>14.62</v>
       </c>
+      <c r="H48" t="n">
+        <v>0.8622127175331116</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.2346485555171967</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1647,13 +1939,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4536862</v>
+        <v>0.4536862003780718</v>
       </c>
       <c r="C49" t="n">
-        <v>0.113851992</v>
+        <v>0.1138519924098672</v>
       </c>
       <c r="D49" t="n">
-        <v>0.423440454</v>
+        <v>0.4234404536862004</v>
       </c>
       <c r="E49" t="n">
         <v>13.5</v>
@@ -1664,6 +1956,12 @@
       <c r="G49" t="n">
         <v>14.22</v>
       </c>
+      <c r="H49" t="n">
+        <v>0.857858419418335</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.2373574823141098</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1672,13 +1970,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.399293286</v>
+        <v>0.3992932862190812</v>
       </c>
       <c r="C50" t="n">
-        <v>0.127659574</v>
+        <v>0.1276595744680851</v>
       </c>
       <c r="D50" t="n">
-        <v>0.367491166</v>
+        <v>0.3674911660777385</v>
       </c>
       <c r="E50" t="n">
         <v>13.9</v>
@@ -1689,6 +1987,12 @@
       <c r="G50" t="n">
         <v>13.41</v>
       </c>
+      <c r="H50" t="n">
+        <v>0.8532969951629639</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.2556425333023071</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1697,13 +2001,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.311926606</v>
+        <v>0.3119266055045872</v>
       </c>
       <c r="C51" t="n">
-        <v>0.05893186</v>
+        <v>0.05893186003683241</v>
       </c>
       <c r="D51" t="n">
-        <v>0.289908257</v>
+        <v>0.2899082568807339</v>
       </c>
       <c r="E51" t="n">
         <v>13.6</v>
@@ -1714,6 +2018,12 @@
       <c r="G51" t="n">
         <v>15.78</v>
       </c>
+      <c r="H51" t="n">
+        <v>0.8348326086997986</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.23113913834095</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1722,10 +2032,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.51875</v>
+        <v>0.5187499999999999</v>
       </c>
       <c r="C52" t="n">
-        <v>0.103448276</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="D52" t="n">
         <v>0.49375</v>
@@ -1739,6 +2049,12 @@
       <c r="G52" t="n">
         <v>14.22</v>
       </c>
+      <c r="H52" t="n">
+        <v>0.8494028449058533</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.2319302260875702</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1747,13 +2063,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.366197183</v>
+        <v>0.3661971830985915</v>
       </c>
       <c r="C53" t="n">
-        <v>0.068686869</v>
+        <v>0.06868686868686869</v>
       </c>
       <c r="D53" t="n">
-        <v>0.317907445</v>
+        <v>0.317907444668008</v>
       </c>
       <c r="E53" t="n">
         <v>13.5</v>
@@ -1764,6 +2080,12 @@
       <c r="G53" t="n">
         <v>13.81</v>
       </c>
+      <c r="H53" t="n">
+        <v>0.8401792645454407</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.2365726828575134</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1772,13 +2094,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.281081081</v>
+        <v>0.2810810810810811</v>
       </c>
       <c r="C54" t="n">
-        <v>0.043399638</v>
+        <v>0.0433996383363472</v>
       </c>
       <c r="D54" t="n">
-        <v>0.266666667</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E54" t="n">
         <v>15.7</v>
@@ -1789,6 +2111,12 @@
       <c r="G54" t="n">
         <v>16.82</v>
       </c>
+      <c r="H54" t="n">
+        <v>0.8319886326789856</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.233376756310463</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1797,13 +2125,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.335423197</v>
+        <v>0.335423197492163</v>
       </c>
       <c r="C55" t="n">
-        <v>0.06918239</v>
+        <v>0.06918238993710692</v>
       </c>
       <c r="D55" t="n">
-        <v>0.310344828</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="E55" t="n">
         <v>19</v>
@@ -1814,6 +2142,12 @@
       <c r="G55" t="n">
         <v>17.3</v>
       </c>
+      <c r="H55" t="n">
+        <v>0.8052234649658203</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.2407791465520859</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1825,7 +2159,7 @@
         <v>0.4256</v>
       </c>
       <c r="C56" t="n">
-        <v>0.096308186</v>
+        <v>0.09630818619582664</v>
       </c>
       <c r="D56" t="n">
         <v>0.4</v>
@@ -1839,6 +2173,12 @@
       <c r="G56" t="n">
         <v>14.33</v>
       </c>
+      <c r="H56" t="n">
+        <v>0.8504911065101624</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.2613275945186615</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1847,13 +2187,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.352490421</v>
+        <v>0.3524904214559387</v>
       </c>
       <c r="C57" t="n">
-        <v>0.092307692</v>
+        <v>0.0923076923076923</v>
       </c>
       <c r="D57" t="n">
-        <v>0.329501916</v>
+        <v>0.3295019157088123</v>
       </c>
       <c r="E57" t="n">
         <v>14.2</v>
@@ -1864,6 +2204,12 @@
       <c r="G57" t="n">
         <v>17.11</v>
       </c>
+      <c r="H57" t="n">
+        <v>0.8496045470237732</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.2581672668457031</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1872,13 +2218,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.394618834</v>
+        <v>0.3946188340807175</v>
       </c>
       <c r="C58" t="n">
-        <v>0.117117117</v>
+        <v>0.1171171171171171</v>
       </c>
       <c r="D58" t="n">
-        <v>0.35426009</v>
+        <v>0.3542600896860987</v>
       </c>
       <c r="E58" t="n">
         <v>12.5</v>
@@ -1889,6 +2235,12 @@
       <c r="G58" t="n">
         <v>12.46</v>
       </c>
+      <c r="H58" t="n">
+        <v>0.8464139103889465</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.2457085251808167</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1897,13 +2249,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.459143969</v>
+        <v>0.4591439688715954</v>
       </c>
       <c r="C59" t="n">
         <v>0.10546875</v>
       </c>
       <c r="D59" t="n">
-        <v>0.408560311</v>
+        <v>0.4085603112840467</v>
       </c>
       <c r="E59" t="n">
         <v>12.2</v>
@@ -1914,6 +2266,12 @@
       <c r="G59" t="n">
         <v>14.79</v>
       </c>
+      <c r="H59" t="n">
+        <v>0.8531395792961121</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.2414892017841339</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1922,13 +2280,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.441005803</v>
+        <v>0.4410058027079304</v>
       </c>
       <c r="C60" t="n">
-        <v>0.104854369</v>
+        <v>0.1048543689320388</v>
       </c>
       <c r="D60" t="n">
-        <v>0.421663443</v>
+        <v>0.4216634429400387</v>
       </c>
       <c r="E60" t="n">
         <v>15.2</v>
@@ -1939,6 +2297,12 @@
       <c r="G60" t="n">
         <v>14.74</v>
       </c>
+      <c r="H60" t="n">
+        <v>0.8404698967933655</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.2242118418216705</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1947,13 +2311,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.369168357</v>
+        <v>0.3691683569979716</v>
       </c>
       <c r="C61" t="n">
-        <v>0.044806517</v>
+        <v>0.04480651731160895</v>
       </c>
       <c r="D61" t="n">
-        <v>0.320486815</v>
+        <v>0.3204868154158215</v>
       </c>
       <c r="E61" t="n">
         <v>16.6</v>
@@ -1964,6 +2328,12 @@
       <c r="G61" t="n">
         <v>17.52</v>
       </c>
+      <c r="H61" t="n">
+        <v>0.8392927646636963</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.221820279955864</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1972,13 +2342,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.367549669</v>
+        <v>0.3675496688741722</v>
       </c>
       <c r="C62" t="n">
-        <v>0.089700997</v>
+        <v>0.08970099667774087</v>
       </c>
       <c r="D62" t="n">
-        <v>0.341059603</v>
+        <v>0.3410596026490066</v>
       </c>
       <c r="E62" t="n">
         <v>12.3</v>
@@ -1989,6 +2359,12 @@
       <c r="G62" t="n">
         <v>12.53</v>
       </c>
+      <c r="H62" t="n">
+        <v>0.8190894722938538</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.2267919331789017</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1997,13 +2373,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.378167641</v>
+        <v>0.378167641325536</v>
       </c>
       <c r="C63" t="n">
-        <v>0.054794521</v>
+        <v>0.05479452054794521</v>
       </c>
       <c r="D63" t="n">
-        <v>0.335282651</v>
+        <v>0.3352826510721247</v>
       </c>
       <c r="E63" t="n">
         <v>13.2</v>
@@ -2014,6 +2390,12 @@
       <c r="G63" t="n">
         <v>15.14</v>
       </c>
+      <c r="H63" t="n">
+        <v>0.840289294719696</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.2637901306152344</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2022,13 +2404,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.494929006</v>
+        <v>0.4949290060851926</v>
       </c>
       <c r="C64" t="n">
-        <v>0.093686354</v>
+        <v>0.09368635437881874</v>
       </c>
       <c r="D64" t="n">
-        <v>0.462474645</v>
+        <v>0.462474645030426</v>
       </c>
       <c r="E64" t="n">
         <v>12.7</v>
@@ -2039,6 +2421,12 @@
       <c r="G64" t="n">
         <v>14.61</v>
       </c>
+      <c r="H64" t="n">
+        <v>0.8597245812416077</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.245094433426857</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2047,13 +2435,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.398601399</v>
+        <v>0.3986013986013986</v>
       </c>
       <c r="C65" t="n">
-        <v>0.080701754</v>
+        <v>0.08070175438596491</v>
       </c>
       <c r="D65" t="n">
-        <v>0.363636364</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="E65" t="n">
         <v>13.8</v>
@@ -2064,6 +2452,12 @@
       <c r="G65" t="n">
         <v>13.18</v>
       </c>
+      <c r="H65" t="n">
+        <v>0.8265482783317566</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.2342202365398407</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2072,13 +2466,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.497064579</v>
+        <v>0.4970645792563601</v>
       </c>
       <c r="C66" t="n">
-        <v>0.090373281</v>
+        <v>0.09037328094302552</v>
       </c>
       <c r="D66" t="n">
-        <v>0.465753425</v>
+        <v>0.4657534246575342</v>
       </c>
       <c r="E66" t="n">
         <v>14.7</v>
@@ -2089,6 +2483,12 @@
       <c r="G66" t="n">
         <v>16.19</v>
       </c>
+      <c r="H66" t="n">
+        <v>0.8569833636283875</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.2527461647987366</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2097,13 +2497,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.44214876</v>
+        <v>0.4421487603305785</v>
       </c>
       <c r="C67" t="n">
-        <v>0.112033195</v>
+        <v>0.1120331950207469</v>
       </c>
       <c r="D67" t="n">
-        <v>0.41322314</v>
+        <v>0.4132231404958678</v>
       </c>
       <c r="E67" t="n">
         <v>12</v>
@@ -2114,6 +2514,12 @@
       <c r="G67" t="n">
         <v>13</v>
       </c>
+      <c r="H67" t="n">
+        <v>0.8552640676498413</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.2386730462312698</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2122,13 +2528,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.387799564</v>
+        <v>0.3877995642701525</v>
       </c>
       <c r="C68" t="n">
-        <v>0.105032823</v>
+        <v>0.1050328227571116</v>
       </c>
       <c r="D68" t="n">
-        <v>0.352941176</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="E68" t="n">
         <v>13.4</v>
@@ -2139,6 +2545,12 @@
       <c r="G68" t="n">
         <v>14.97</v>
       </c>
+      <c r="H68" t="n">
+        <v>0.8407619595527649</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.2377295196056366</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2147,13 +2559,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.36329588</v>
+        <v>0.3632958801498128</v>
       </c>
       <c r="C69" t="n">
-        <v>0.04887218</v>
+        <v>0.04887218045112782</v>
       </c>
       <c r="D69" t="n">
-        <v>0.31835206</v>
+        <v>0.3183520599250936</v>
       </c>
       <c r="E69" t="n">
         <v>17.3</v>
@@ -2164,6 +2576,12 @@
       <c r="G69" t="n">
         <v>17.46</v>
       </c>
+      <c r="H69" t="n">
+        <v>0.8388538956642151</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.2222511768341064</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2172,13 +2590,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.365248227</v>
+        <v>0.3652482269503546</v>
       </c>
       <c r="C70" t="n">
-        <v>0.081850534</v>
+        <v>0.08185053380782917</v>
       </c>
       <c r="D70" t="n">
-        <v>0.358156028</v>
+        <v>0.3581560283687943</v>
       </c>
       <c r="E70" t="n">
         <v>15.5</v>
@@ -2189,6 +2607,12 @@
       <c r="G70" t="n">
         <v>17.06</v>
       </c>
+      <c r="H70" t="n">
+        <v>0.8371569514274597</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.2440544366836548</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2197,13 +2621,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.300729927</v>
+        <v>0.3007299270072993</v>
       </c>
       <c r="C71" t="n">
-        <v>0.073206442</v>
+        <v>0.07320644216691069</v>
       </c>
       <c r="D71" t="n">
-        <v>0.286131387</v>
+        <v>0.2861313868613138</v>
       </c>
       <c r="E71" t="n">
         <v>15.3</v>
@@ -2214,6 +2638,12 @@
       <c r="G71" t="n">
         <v>14.74</v>
       </c>
+      <c r="H71" t="n">
+        <v>0.822109043598175</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.2415962368249893</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2222,13 +2652,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.390715667</v>
+        <v>0.3907156673114121</v>
       </c>
       <c r="C72" t="n">
-        <v>0.097087379</v>
+        <v>0.0970873786407767</v>
       </c>
       <c r="D72" t="n">
-        <v>0.348162476</v>
+        <v>0.3481624758220503</v>
       </c>
       <c r="E72" t="n">
         <v>15.3</v>
@@ -2239,6 +2669,12 @@
       <c r="G72" t="n">
         <v>15.03</v>
       </c>
+      <c r="H72" t="n">
+        <v>0.8448734879493713</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.2409387677907944</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2247,13 +2683,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.431034483</v>
+        <v>0.4310344827586206</v>
       </c>
       <c r="C73" t="n">
-        <v>0.086580087</v>
+        <v>0.08658008658008658</v>
       </c>
       <c r="D73" t="n">
-        <v>0.400862069</v>
+        <v>0.4008620689655173</v>
       </c>
       <c r="E73" t="n">
         <v>16.4</v>
@@ -2264,6 +2700,12 @@
       <c r="G73" t="n">
         <v>14.74</v>
       </c>
+      <c r="H73" t="n">
+        <v>0.8536101579666138</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.2187176793813705</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2272,13 +2714,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.448210923</v>
+        <v>0.4482109227871939</v>
       </c>
       <c r="C74" t="n">
-        <v>0.177693762</v>
+        <v>0.1776937618147448</v>
       </c>
       <c r="D74" t="n">
-        <v>0.429378531</v>
+        <v>0.4293785310734463</v>
       </c>
       <c r="E74" t="n">
         <v>14.3</v>
@@ -2289,6 +2731,12 @@
       <c r="G74" t="n">
         <v>15.79</v>
       </c>
+      <c r="H74" t="n">
+        <v>0.8568190932273865</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.2365664541721344</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2297,13 +2745,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.438596491</v>
+        <v>0.4385964912280702</v>
       </c>
       <c r="C75" t="n">
-        <v>0.105726872</v>
+        <v>0.105726872246696</v>
       </c>
       <c r="D75" t="n">
-        <v>0.412280702</v>
+        <v>0.412280701754386</v>
       </c>
       <c r="E75" t="n">
         <v>10.2</v>
@@ -2314,6 +2762,12 @@
       <c r="G75" t="n">
         <v>13.05</v>
       </c>
+      <c r="H75" t="n">
+        <v>0.8658277988433838</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.2418444007635117</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2322,13 +2776,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.456942004</v>
+        <v>0.4569420035149385</v>
       </c>
       <c r="C76" t="n">
-        <v>0.08465608500000001</v>
+        <v>0.08465608465608465</v>
       </c>
       <c r="D76" t="n">
-        <v>0.407732865</v>
+        <v>0.4077328646748682</v>
       </c>
       <c r="E76" t="n">
         <v>14.3</v>
@@ -2339,6 +2793,12 @@
       <c r="G76" t="n">
         <v>13.06</v>
       </c>
+      <c r="H76" t="n">
+        <v>0.8505741357803345</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.2422575801610947</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2347,13 +2807,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.405186386</v>
+        <v>0.4051863857374392</v>
       </c>
       <c r="C77" t="n">
-        <v>0.058536585</v>
+        <v>0.05853658536585366</v>
       </c>
       <c r="D77" t="n">
-        <v>0.366288493</v>
+        <v>0.366288492706645</v>
       </c>
       <c r="E77" t="n">
         <v>16.2</v>
@@ -2364,6 +2824,12 @@
       <c r="G77" t="n">
         <v>18.1</v>
       </c>
+      <c r="H77" t="n">
+        <v>0.8372708559036255</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.2364872694015503</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2372,13 +2838,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.344013491</v>
+        <v>0.3440134907251264</v>
       </c>
       <c r="C78" t="n">
-        <v>0.115059222</v>
+        <v>0.1150592216582064</v>
       </c>
       <c r="D78" t="n">
-        <v>0.323777403</v>
+        <v>0.3237774030354131</v>
       </c>
       <c r="E78" t="n">
         <v>14.9</v>
@@ -2389,6 +2855,12 @@
       <c r="G78" t="n">
         <v>15.15</v>
       </c>
+      <c r="H78" t="n">
+        <v>0.8266227841377258</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.2332839071750641</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2397,13 +2869,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.400817996</v>
+        <v>0.4008179959100205</v>
       </c>
       <c r="C79" t="n">
-        <v>0.131416838</v>
+        <v>0.1314168377823409</v>
       </c>
       <c r="D79" t="n">
-        <v>0.372188139</v>
+        <v>0.3721881390593048</v>
       </c>
       <c r="E79" t="n">
         <v>12</v>
@@ -2414,6 +2886,12 @@
       <c r="G79" t="n">
         <v>13.63</v>
       </c>
+      <c r="H79" t="n">
+        <v>0.8474818468093872</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.2575826644897461</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2422,10 +2900,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.422857143</v>
+        <v>0.4228571428571429</v>
       </c>
       <c r="C80" t="n">
-        <v>0.09942638600000001</v>
+        <v>0.0994263862332696</v>
       </c>
       <c r="D80" t="n">
         <v>0.4</v>
@@ -2439,6 +2917,12 @@
       <c r="G80" t="n">
         <v>15.79</v>
       </c>
+      <c r="H80" t="n">
+        <v>0.8495208621025085</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.2269905358552933</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2447,13 +2931,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.461818182</v>
+        <v>0.4618181818181818</v>
       </c>
       <c r="C81" t="n">
-        <v>0.098540146</v>
+        <v>0.09854014598540146</v>
       </c>
       <c r="D81" t="n">
-        <v>0.436363636</v>
+        <v>0.4363636363636363</v>
       </c>
       <c r="E81" t="n">
         <v>13.2</v>
@@ -2464,6 +2948,12 @@
       <c r="G81" t="n">
         <v>13.64</v>
       </c>
+      <c r="H81" t="n">
+        <v>0.855344831943512</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.2382205575704575</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2472,13 +2962,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.472103004</v>
+        <v>0.4721030042918455</v>
       </c>
       <c r="C82" t="n">
-        <v>0.155172414</v>
+        <v>0.1551724137931035</v>
       </c>
       <c r="D82" t="n">
-        <v>0.407725322</v>
+        <v>0.407725321888412</v>
       </c>
       <c r="E82" t="n">
         <v>12.5</v>
@@ -2489,6 +2979,12 @@
       <c r="G82" t="n">
         <v>13.63</v>
       </c>
+      <c r="H82" t="n">
+        <v>0.8586909770965576</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.228706493973732</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2497,13 +2993,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.405904059</v>
+        <v>0.4059040590405904</v>
       </c>
       <c r="C83" t="n">
-        <v>0.125925926</v>
+        <v>0.1259259259259259</v>
       </c>
       <c r="D83" t="n">
-        <v>0.372693727</v>
+        <v>0.3726937269372694</v>
       </c>
       <c r="E83" t="n">
         <v>10.9</v>
@@ -2514,6 +3010,12 @@
       <c r="G83" t="n">
         <v>12.02</v>
       </c>
+      <c r="H83" t="n">
+        <v>0.8474199771881104</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.2295558750629425</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2522,13 +3024,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.412244898</v>
+        <v>0.4122448979591837</v>
       </c>
       <c r="C84" t="n">
-        <v>0.094262295</v>
+        <v>0.09426229508196721</v>
       </c>
       <c r="D84" t="n">
-        <v>0.375510204</v>
+        <v>0.3755102040816327</v>
       </c>
       <c r="E84" t="n">
         <v>14.5</v>
@@ -2539,6 +3041,12 @@
       <c r="G84" t="n">
         <v>16.02</v>
       </c>
+      <c r="H84" t="n">
+        <v>0.8524827361106873</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.2284386605024338</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2547,13 +3055,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.404347826</v>
+        <v>0.4043478260869565</v>
       </c>
       <c r="C85" t="n">
-        <v>0.061135371</v>
+        <v>0.0611353711790393</v>
       </c>
       <c r="D85" t="n">
-        <v>0.373913043</v>
+        <v>0.3739130434782609</v>
       </c>
       <c r="E85" t="n">
         <v>11.4</v>
@@ -2564,6 +3072,12 @@
       <c r="G85" t="n">
         <v>13.34</v>
       </c>
+      <c r="H85" t="n">
+        <v>0.8502365350723267</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.2371463775634766</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2572,13 +3086,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.336633663</v>
+        <v>0.3366336633663366</v>
       </c>
       <c r="C86" t="n">
-        <v>0.051689861</v>
+        <v>0.05168986083499006</v>
       </c>
       <c r="D86" t="n">
-        <v>0.297029703</v>
+        <v>0.297029702970297</v>
       </c>
       <c r="E86" t="n">
         <v>13.2</v>
@@ -2589,6 +3103,12 @@
       <c r="G86" t="n">
         <v>13.81</v>
       </c>
+      <c r="H86" t="n">
+        <v>0.8339864015579224</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.2417447417974472</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2597,13 +3117,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.447058824</v>
+        <v>0.4470588235294118</v>
       </c>
       <c r="C87" t="n">
-        <v>0.123893805</v>
+        <v>0.1238938053097345</v>
       </c>
       <c r="D87" t="n">
-        <v>0.420588235</v>
+        <v>0.4205882352941177</v>
       </c>
       <c r="E87" t="n">
         <v>16.9</v>
@@ -2614,6 +3134,12 @@
       <c r="G87" t="n">
         <v>16.19</v>
       </c>
+      <c r="H87" t="n">
+        <v>0.8315678238868713</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.2412514686584473</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2622,13 +3148,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.330033003</v>
+        <v>0.33003300330033</v>
       </c>
       <c r="C88" t="n">
-        <v>0.059602649</v>
+        <v>0.05960264900662252</v>
       </c>
       <c r="D88" t="n">
-        <v>0.310231023</v>
+        <v>0.3102310231023103</v>
       </c>
       <c r="E88" t="n">
         <v>13.5</v>
@@ -2639,6 +3165,12 @@
       <c r="G88" t="n">
         <v>15.84</v>
       </c>
+      <c r="H88" t="n">
+        <v>0.8408252596855164</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.2525214552879333</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2647,13 +3179,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.392785571</v>
+        <v>0.3927855711422845</v>
       </c>
       <c r="C89" t="n">
-        <v>0.108651911</v>
+        <v>0.1086519114688129</v>
       </c>
       <c r="D89" t="n">
-        <v>0.356713427</v>
+        <v>0.3567134268537074</v>
       </c>
       <c r="E89" t="n">
         <v>12.7</v>
@@ -2664,6 +3196,12 @@
       <c r="G89" t="n">
         <v>12.65</v>
       </c>
+      <c r="H89" t="n">
+        <v>0.8582003712654114</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.2524770796298981</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2672,13 +3210,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.468619247</v>
+        <v>0.4686192468619247</v>
       </c>
       <c r="C90" t="n">
-        <v>0.08403361299999999</v>
+        <v>0.08403361344537816</v>
       </c>
       <c r="D90" t="n">
-        <v>0.435146444</v>
+        <v>0.4351464435146444</v>
       </c>
       <c r="E90" t="n">
         <v>13.3</v>
@@ -2689,6 +3227,12 @@
       <c r="G90" t="n">
         <v>14.34</v>
       </c>
+      <c r="H90" t="n">
+        <v>0.8413558006286621</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.2233688682317734</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2697,13 +3241,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.447058824</v>
+        <v>0.4470588235294118</v>
       </c>
       <c r="C91" t="n">
-        <v>0.141843972</v>
+        <v>0.1418439716312057</v>
       </c>
       <c r="D91" t="n">
-        <v>0.414117647</v>
+        <v>0.4141176470588235</v>
       </c>
       <c r="E91" t="n">
         <v>12.2</v>
@@ -2714,6 +3258,12 @@
       <c r="G91" t="n">
         <v>13.75</v>
       </c>
+      <c r="H91" t="n">
+        <v>0.8561061024665833</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.2233797013759613</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2722,13 +3272,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.302828619</v>
+        <v>0.302828618968386</v>
       </c>
       <c r="C92" t="n">
-        <v>0.063439065</v>
+        <v>0.06343906510851419</v>
       </c>
       <c r="D92" t="n">
-        <v>0.282861897</v>
+        <v>0.2828618968386024</v>
       </c>
       <c r="E92" t="n">
         <v>12.7</v>
@@ -2739,6 +3289,12 @@
       <c r="G92" t="n">
         <v>14.56</v>
       </c>
+      <c r="H92" t="n">
+        <v>0.8221038579940796</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.2388069927692413</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2747,13 +3303,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.434782609</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="C93" t="n">
-        <v>0.07936507900000001</v>
+        <v>0.07936507936507937</v>
       </c>
       <c r="D93" t="n">
-        <v>0.399209486</v>
+        <v>0.3992094861660079</v>
       </c>
       <c r="E93" t="n">
         <v>13.4</v>
@@ -2764,6 +3320,12 @@
       <c r="G93" t="n">
         <v>13.92</v>
       </c>
+      <c r="H93" t="n">
+        <v>0.8514309525489807</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.2522016763687134</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2772,13 +3334,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.429840142</v>
+        <v>0.4298401420959148</v>
       </c>
       <c r="C94" t="n">
-        <v>0.08199643500000001</v>
+        <v>0.08199643493761141</v>
       </c>
       <c r="D94" t="n">
-        <v>0.394316163</v>
+        <v>0.394316163410302</v>
       </c>
       <c r="E94" t="n">
         <v>12.3</v>
@@ -2789,6 +3351,12 @@
       <c r="G94" t="n">
         <v>11.9</v>
       </c>
+      <c r="H94" t="n">
+        <v>0.8421248197555542</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.2382459938526154</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2797,13 +3365,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.41322314</v>
+        <v>0.4132231404958677</v>
       </c>
       <c r="C95" t="n">
-        <v>0.091286307</v>
+        <v>0.09128630705394192</v>
       </c>
       <c r="D95" t="n">
-        <v>0.367768595</v>
+        <v>0.3677685950413223</v>
       </c>
       <c r="E95" t="n">
         <v>16.1</v>
@@ -2814,6 +3382,12 @@
       <c r="G95" t="n">
         <v>16.42</v>
       </c>
+      <c r="H95" t="n">
+        <v>0.8430431485176086</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.2218773812055588</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2822,10 +3396,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.417391304</v>
+        <v>0.4173913043478261</v>
       </c>
       <c r="C96" t="n">
-        <v>0.096069869</v>
+        <v>0.09606986899563319</v>
       </c>
       <c r="D96" t="n">
         <v>0.4</v>
@@ -2839,6 +3413,12 @@
       <c r="G96" t="n">
         <v>14.16</v>
       </c>
+      <c r="H96" t="n">
+        <v>0.8470350503921509</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.22886623442173</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2847,13 +3427,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.391472868</v>
+        <v>0.3914728682170542</v>
       </c>
       <c r="C97" t="n">
-        <v>0.124513619</v>
+        <v>0.1245136186770428</v>
       </c>
       <c r="D97" t="n">
-        <v>0.372093023</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="E97" t="n">
         <v>18.1</v>
@@ -2864,6 +3444,12 @@
       <c r="G97" t="n">
         <v>17.35</v>
       </c>
+      <c r="H97" t="n">
+        <v>0.852499783039093</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.244356170296669</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2872,13 +3458,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.382113821</v>
+        <v>0.3821138211382114</v>
       </c>
       <c r="C98" t="n">
-        <v>0.097959184</v>
+        <v>0.09795918367346938</v>
       </c>
       <c r="D98" t="n">
-        <v>0.369918699</v>
+        <v>0.3699186991869919</v>
       </c>
       <c r="E98" t="n">
         <v>15.6</v>
@@ -2889,6 +3475,12 @@
       <c r="G98" t="n">
         <v>15.96</v>
       </c>
+      <c r="H98" t="n">
+        <v>0.8513687252998352</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.2296577990055084</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2897,13 +3489,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.45174538</v>
+        <v>0.4517453798767967</v>
       </c>
       <c r="C99" t="n">
-        <v>0.057731959</v>
+        <v>0.05773195876288659</v>
       </c>
       <c r="D99" t="n">
-        <v>0.410677618</v>
+        <v>0.4106776180698152</v>
       </c>
       <c r="E99" t="n">
         <v>13.6</v>
@@ -2914,6 +3506,12 @@
       <c r="G99" t="n">
         <v>14.1</v>
       </c>
+      <c r="H99" t="n">
+        <v>0.8466266393661499</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.2305517941713333</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2922,13 +3520,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.34015748</v>
+        <v>0.3401574803149607</v>
       </c>
       <c r="C100" t="n">
-        <v>0.07898894200000001</v>
+        <v>0.07898894154818326</v>
       </c>
       <c r="D100" t="n">
-        <v>0.305511811</v>
+        <v>0.3055118110236221</v>
       </c>
       <c r="E100" t="n">
         <v>14.1</v>
@@ -2939,6 +3537,12 @@
       <c r="G100" t="n">
         <v>14.27</v>
       </c>
+      <c r="H100" t="n">
+        <v>0.8263896703720093</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.2346080094575882</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2947,13 +3551,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.367201426</v>
+        <v>0.3672014260249554</v>
       </c>
       <c r="C101" t="n">
-        <v>0.06797853299999999</v>
+        <v>0.06797853309481217</v>
       </c>
       <c r="D101" t="n">
-        <v>0.335115865</v>
+        <v>0.3351158645276293</v>
       </c>
       <c r="E101" t="n">
         <v>15.4</v>
@@ -2964,6 +3568,12 @@
       <c r="G101" t="n">
         <v>16.24</v>
       </c>
+      <c r="H101" t="n">
+        <v>0.8484952449798584</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.2339090555906296</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2972,13 +3582,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.378478664</v>
+        <v>0.37847866419295</v>
       </c>
       <c r="C102" t="n">
-        <v>0.100558659</v>
+        <v>0.1005586592178771</v>
       </c>
       <c r="D102" t="n">
-        <v>0.367346939</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="E102" t="n">
         <v>14.2</v>
@@ -2989,6 +3599,12 @@
       <c r="G102" t="n">
         <v>13.98</v>
       </c>
+      <c r="H102" t="n">
+        <v>0.8509999513626099</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.2517678737640381</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2997,13 +3613,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.342541436</v>
+        <v>0.3425414364640884</v>
       </c>
       <c r="C103" t="n">
-        <v>0.06284658</v>
+        <v>0.06284658040665435</v>
       </c>
       <c r="D103" t="n">
-        <v>0.305709024</v>
+        <v>0.3057090239410681</v>
       </c>
       <c r="E103" t="n">
         <v>10.8</v>
@@ -3014,6 +3630,12 @@
       <c r="G103" t="n">
         <v>13.28</v>
       </c>
+      <c r="H103" t="n">
+        <v>0.8426968455314636</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.3048933446407318</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3022,13 +3644,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.375286041</v>
+        <v>0.3752860411899313</v>
       </c>
       <c r="C104" t="n">
-        <v>0.091954023</v>
+        <v>0.09195402298850575</v>
       </c>
       <c r="D104" t="n">
-        <v>0.352402746</v>
+        <v>0.3524027459954234</v>
       </c>
       <c r="E104" t="n">
         <v>13.6</v>
@@ -3039,6 +3661,12 @@
       <c r="G104" t="n">
         <v>14.21</v>
       </c>
+      <c r="H104" t="n">
+        <v>0.839785099029541</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.2303995043039322</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3047,13 +3675,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.352293578</v>
+        <v>0.3522935779816513</v>
       </c>
       <c r="C105" t="n">
-        <v>0.055248619</v>
+        <v>0.05524861878453039</v>
       </c>
       <c r="D105" t="n">
-        <v>0.326605505</v>
+        <v>0.326605504587156</v>
       </c>
       <c r="E105" t="n">
         <v>17.1</v>
@@ -3064,6 +3692,12 @@
       <c r="G105" t="n">
         <v>17.82</v>
       </c>
+      <c r="H105" t="n">
+        <v>0.8327401280403137</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.2313291728496552</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3072,13 +3706,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.283387622</v>
+        <v>0.2833876221498371</v>
       </c>
       <c r="C106" t="n">
-        <v>0.08169934600000001</v>
+        <v>0.08169934640522875</v>
       </c>
       <c r="D106" t="n">
-        <v>0.260586319</v>
+        <v>0.260586319218241</v>
       </c>
       <c r="E106" t="n">
         <v>11.8</v>
@@ -3089,6 +3723,12 @@
       <c r="G106" t="n">
         <v>14.68</v>
       </c>
+      <c r="H106" t="n">
+        <v>0.8249893188476562</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.2516097724437714</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3100,10 +3740,10 @@
         <v>0.45</v>
       </c>
       <c r="C107" t="n">
-        <v>0.132420091</v>
+        <v>0.1324200913242009</v>
       </c>
       <c r="D107" t="n">
-        <v>0.395454545</v>
+        <v>0.3954545454545454</v>
       </c>
       <c r="E107" t="n">
         <v>12</v>
@@ -3114,6 +3754,12 @@
       <c r="G107" t="n">
         <v>13.52</v>
       </c>
+      <c r="H107" t="n">
+        <v>0.8505359292030334</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.2251090556383133</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3122,13 +3768,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.373225152</v>
+        <v>0.3732251521298174</v>
       </c>
       <c r="C108" t="n">
-        <v>0.093686354</v>
+        <v>0.09368635437881873</v>
       </c>
       <c r="D108" t="n">
-        <v>0.336713996</v>
+        <v>0.3367139959432049</v>
       </c>
       <c r="E108" t="n">
         <v>14.7</v>
@@ -3139,6 +3785,12 @@
       <c r="G108" t="n">
         <v>15.61</v>
       </c>
+      <c r="H108" t="n">
+        <v>0.8462607860565186</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.2353733777999878</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3147,13 +3799,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.365553603</v>
+        <v>0.3655536028119508</v>
       </c>
       <c r="C109" t="n">
-        <v>0.063492063</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="D109" t="n">
-        <v>0.319859402</v>
+        <v>0.3198594024604569</v>
       </c>
       <c r="E109" t="n">
         <v>16.6</v>
@@ -3164,6 +3816,12 @@
       <c r="G109" t="n">
         <v>17.35</v>
       </c>
+      <c r="H109" t="n">
+        <v>0.8309469223022461</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.2351029813289642</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3172,13 +3830,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.437619962</v>
+        <v>0.4376199616122841</v>
       </c>
       <c r="C110" t="n">
-        <v>0.077071291</v>
+        <v>0.07707129094412329</v>
       </c>
       <c r="D110" t="n">
-        <v>0.406909789</v>
+        <v>0.4069097888675624</v>
       </c>
       <c r="E110" t="n">
         <v>12.9</v>
@@ -3189,6 +3847,12 @@
       <c r="G110" t="n">
         <v>14.27</v>
       </c>
+      <c r="H110" t="n">
+        <v>0.8444511294364929</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.2299273312091827</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3197,13 +3861,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.436525612</v>
+        <v>0.4365256124721604</v>
       </c>
       <c r="C111" t="n">
-        <v>0.067114094</v>
+        <v>0.06711409395973154</v>
       </c>
       <c r="D111" t="n">
-        <v>0.418708241</v>
+        <v>0.4187082405345212</v>
       </c>
       <c r="E111" t="n">
         <v>10.5</v>
@@ -3214,6 +3878,12 @@
       <c r="G111" t="n">
         <v>11.37</v>
       </c>
+      <c r="H111" t="n">
+        <v>0.849571168422699</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.2275761663913727</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3222,13 +3892,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.416184971</v>
+        <v>0.4161849710982659</v>
       </c>
       <c r="C112" t="n">
-        <v>0.113043478</v>
+        <v>0.1130434782608696</v>
       </c>
       <c r="D112" t="n">
-        <v>0.38150289</v>
+        <v>0.3815028901734104</v>
       </c>
       <c r="E112" t="n">
         <v>14.2</v>
@@ -3239,6 +3909,12 @@
       <c r="G112" t="n">
         <v>15.9</v>
       </c>
+      <c r="H112" t="n">
+        <v>0.8449170589447021</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.2556467354297638</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3247,13 +3923,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.406072106</v>
+        <v>0.4060721062618596</v>
       </c>
       <c r="C113" t="n">
-        <v>0.106666667</v>
+        <v>0.1066666666666667</v>
       </c>
       <c r="D113" t="n">
-        <v>0.394686907</v>
+        <v>0.3946869070208729</v>
       </c>
       <c r="E113" t="n">
         <v>13.7</v>
@@ -3264,6 +3940,12 @@
       <c r="G113" t="n">
         <v>14.45</v>
       </c>
+      <c r="H113" t="n">
+        <v>0.8463650941848755</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.2504838705062866</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3272,13 +3954,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.380136986</v>
+        <v>0.3801369863013699</v>
       </c>
       <c r="C114" t="n">
-        <v>0.144329897</v>
+        <v>0.1443298969072165</v>
       </c>
       <c r="D114" t="n">
-        <v>0.359589041</v>
+        <v>0.3595890410958904</v>
       </c>
       <c r="E114" t="n">
         <v>11.5</v>
@@ -3289,6 +3971,12 @@
       <c r="G114" t="n">
         <v>11.78</v>
       </c>
+      <c r="H114" t="n">
+        <v>0.8412694931030273</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.295029878616333</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3297,13 +3985,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.343042071</v>
+        <v>0.343042071197411</v>
       </c>
       <c r="C115" t="n">
-        <v>0.090909091</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="D115" t="n">
-        <v>0.310679612</v>
+        <v>0.3106796116504854</v>
       </c>
       <c r="E115" t="n">
         <v>11.4</v>
@@ -3314,6 +4002,12 @@
       <c r="G115" t="n">
         <v>14.61</v>
       </c>
+      <c r="H115" t="n">
+        <v>0.8386867642402649</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.2713243365287781</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3322,13 +4016,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.406844106</v>
+        <v>0.4068441064638783</v>
       </c>
       <c r="C116" t="n">
-        <v>0.103053435</v>
+        <v>0.1030534351145038</v>
       </c>
       <c r="D116" t="n">
-        <v>0.365019011</v>
+        <v>0.3650190114068442</v>
       </c>
       <c r="E116" t="n">
         <v>13.3</v>
@@ -3339,6 +4033,12 @@
       <c r="G116" t="n">
         <v>14.97</v>
       </c>
+      <c r="H116" t="n">
+        <v>0.8470567464828491</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.255195140838623</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3347,13 +4047,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.369863014</v>
+        <v>0.3698630136986301</v>
       </c>
       <c r="C117" t="n">
-        <v>0.134020619</v>
+        <v>0.134020618556701</v>
       </c>
       <c r="D117" t="n">
-        <v>0.332191781</v>
+        <v>0.3321917808219178</v>
       </c>
       <c r="E117" t="n">
         <v>12.3</v>
@@ -3364,6 +4064,12 @@
       <c r="G117" t="n">
         <v>11.55</v>
       </c>
+      <c r="H117" t="n">
+        <v>0.8460561037063599</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.2299993336200714</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3372,13 +4078,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.328519856</v>
+        <v>0.3285198555956679</v>
       </c>
       <c r="C118" t="n">
-        <v>0.08695652199999999</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="D118" t="n">
-        <v>0.296028881</v>
+        <v>0.296028880866426</v>
       </c>
       <c r="E118" t="n">
         <v>14.1</v>
@@ -3389,6 +4095,12 @@
       <c r="G118" t="n">
         <v>16.13</v>
       </c>
+      <c r="H118" t="n">
+        <v>0.8538092970848083</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.2606611847877502</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3397,13 +4109,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.464579901</v>
+        <v>0.4645799011532125</v>
       </c>
       <c r="C119" t="n">
-        <v>0.12892562</v>
+        <v>0.1289256198347107</v>
       </c>
       <c r="D119" t="n">
-        <v>0.421746293</v>
+        <v>0.4217462932454695</v>
       </c>
       <c r="E119" t="n">
         <v>16.4</v>
@@ -3414,6 +4126,12 @@
       <c r="G119" t="n">
         <v>16.25</v>
       </c>
+      <c r="H119" t="n">
+        <v>0.8533846139907837</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.246280774474144</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3422,13 +4140,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.408544726</v>
+        <v>0.4085447263017357</v>
       </c>
       <c r="C120" t="n">
-        <v>0.096385542</v>
+        <v>0.09638554216867469</v>
       </c>
       <c r="D120" t="n">
-        <v>0.397863818</v>
+        <v>0.3978638184245661</v>
       </c>
       <c r="E120" t="n">
         <v>14.2</v>
@@ -3439,6 +4157,12 @@
       <c r="G120" t="n">
         <v>14.97</v>
       </c>
+      <c r="H120" t="n">
+        <v>0.8239029049873352</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.2382771670818329</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3447,13 +4171,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.358974359</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="C121" t="n">
-        <v>0.06088993</v>
+        <v>0.06088992974238877</v>
       </c>
       <c r="D121" t="n">
-        <v>0.331002331</v>
+        <v>0.331002331002331</v>
       </c>
       <c r="E121" t="n">
         <v>12.8</v>
@@ -3464,6 +4188,12 @@
       <c r="G121" t="n">
         <v>15.14</v>
       </c>
+      <c r="H121" t="n">
+        <v>0.8471146821975708</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.2326601296663284</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3472,10 +4202,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.461309524</v>
+        <v>0.4613095238095238</v>
       </c>
       <c r="C122" t="n">
-        <v>0.143283582</v>
+        <v>0.1432835820895522</v>
       </c>
       <c r="D122" t="n">
         <v>0.4375</v>
@@ -3489,6 +4219,12 @@
       <c r="G122" t="n">
         <v>15.03</v>
       </c>
+      <c r="H122" t="n">
+        <v>0.8426831364631653</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.2316845655441284</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3497,13 +4233,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.464174455</v>
+        <v>0.4641744548286604</v>
       </c>
       <c r="C123" t="n">
         <v>0.103125</v>
       </c>
       <c r="D123" t="n">
-        <v>0.445482866</v>
+        <v>0.4454828660436137</v>
       </c>
       <c r="E123" t="n">
         <v>14.3</v>
@@ -3514,6 +4250,12 @@
       <c r="G123" t="n">
         <v>13.58</v>
       </c>
+      <c r="H123" t="n">
+        <v>0.8405880331993103</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.2466210573911667</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3522,13 +4264,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.360465116</v>
+        <v>0.3604651162790699</v>
       </c>
       <c r="C124" t="n">
-        <v>0.08560311299999999</v>
+        <v>0.08560311284046693</v>
       </c>
       <c r="D124" t="n">
-        <v>0.329457364</v>
+        <v>0.3294573643410853</v>
       </c>
       <c r="E124" t="n">
         <v>15.2</v>
@@ -3539,6 +4281,12 @@
       <c r="G124" t="n">
         <v>14.86</v>
       </c>
+      <c r="H124" t="n">
+        <v>0.841808021068573</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.2471832484006882</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3547,10 +4295,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.412037037</v>
+        <v>0.412037037037037</v>
       </c>
       <c r="C125" t="n">
-        <v>0.055813953</v>
+        <v>0.05581395348837209</v>
       </c>
       <c r="D125" t="n">
         <v>0.375</v>
@@ -3564,6 +4312,12 @@
       <c r="G125" t="n">
         <v>15.26</v>
       </c>
+      <c r="H125" t="n">
+        <v>0.8405863642692566</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.2330288887023926</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3572,13 +4326,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.363901019</v>
+        <v>0.363901018922853</v>
       </c>
       <c r="C126" t="n">
-        <v>0.116788321</v>
+        <v>0.1167883211678832</v>
       </c>
       <c r="D126" t="n">
-        <v>0.334788937</v>
+        <v>0.3347889374090247</v>
       </c>
       <c r="E126" t="n">
         <v>13.2</v>
@@ -3589,6 +4343,12 @@
       <c r="G126" t="n">
         <v>14.97</v>
       </c>
+      <c r="H126" t="n">
+        <v>0.8251211643218994</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.2528496980667114</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3597,13 +4357,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.446043165</v>
+        <v>0.4460431654676258</v>
       </c>
       <c r="C127" t="n">
-        <v>0.144404332</v>
+        <v>0.1444043321299639</v>
       </c>
       <c r="D127" t="n">
-        <v>0.424460432</v>
+        <v>0.4244604316546762</v>
       </c>
       <c r="E127" t="n">
         <v>16</v>
@@ -3614,6 +4374,12 @@
       <c r="G127" t="n">
         <v>15.21</v>
       </c>
+      <c r="H127" t="n">
+        <v>0.8572494983673096</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.2450228333473206</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3622,13 +4388,13 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.35701275</v>
+        <v>0.3570127504553734</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0511883</v>
+        <v>0.05118829981718464</v>
       </c>
       <c r="D128" t="n">
-        <v>0.327868852</v>
+        <v>0.3278688524590164</v>
       </c>
       <c r="E128" t="n">
         <v>13.5</v>
@@ -3639,6 +4405,12 @@
       <c r="G128" t="n">
         <v>14.39</v>
       </c>
+      <c r="H128" t="n">
+        <v>0.8325035572052002</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.2469556331634521</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3647,13 +4419,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.355987055</v>
+        <v>0.3559870550161812</v>
       </c>
       <c r="C129" t="n">
-        <v>0.058441558</v>
+        <v>0.05844155844155845</v>
       </c>
       <c r="D129" t="n">
-        <v>0.310679612</v>
+        <v>0.3106796116504855</v>
       </c>
       <c r="E129" t="n">
         <v>10.3</v>
@@ -3664,6 +4436,12 @@
       <c r="G129" t="n">
         <v>12.13</v>
       </c>
+      <c r="H129" t="n">
+        <v>0.8322170972824097</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.2440231144428253</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3672,13 +4450,13 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.376599634</v>
+        <v>0.376599634369287</v>
       </c>
       <c r="C130" t="n">
-        <v>0.073394495</v>
+        <v>0.07339449541284404</v>
       </c>
       <c r="D130" t="n">
-        <v>0.347349177</v>
+        <v>0.3473491773308958</v>
       </c>
       <c r="E130" t="n">
         <v>12.3</v>
@@ -3689,6 +4467,12 @@
       <c r="G130" t="n">
         <v>13.8</v>
       </c>
+      <c r="H130" t="n">
+        <v>0.8427404761314392</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.2386998534202576</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3697,13 +4481,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.359683794</v>
+        <v>0.3596837944664032</v>
       </c>
       <c r="C131" t="n">
-        <v>0.071428571</v>
+        <v>0.07142857142857144</v>
       </c>
       <c r="D131" t="n">
-        <v>0.339920949</v>
+        <v>0.3399209486166008</v>
       </c>
       <c r="E131" t="n">
         <v>9.199999999999999</v>
@@ -3714,6 +4498,12 @@
       <c r="G131" t="n">
         <v>11.82</v>
       </c>
+      <c r="H131" t="n">
+        <v>0.8330429196357727</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.2459913343191147</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3722,10 +4512,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.313333333</v>
+        <v>0.3133333333333333</v>
       </c>
       <c r="C132" t="n">
-        <v>0.033444816</v>
+        <v>0.0334448160535117</v>
       </c>
       <c r="D132" t="n">
         <v>0.29</v>
@@ -3739,6 +4529,12 @@
       <c r="G132" t="n">
         <v>15.37</v>
       </c>
+      <c r="H132" t="n">
+        <v>0.8212146162986755</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.2703057527542114</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3747,13 +4543,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.412256267</v>
+        <v>0.4122562674094708</v>
       </c>
       <c r="C133" t="n">
-        <v>0.072829132</v>
+        <v>0.07282913165266106</v>
       </c>
       <c r="D133" t="n">
-        <v>0.373259053</v>
+        <v>0.3732590529247911</v>
       </c>
       <c r="E133" t="n">
         <v>13.1</v>
@@ -3764,6 +4560,12 @@
       <c r="G133" t="n">
         <v>15.43</v>
       </c>
+      <c r="H133" t="n">
+        <v>0.8609074354171753</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.2214328944683075</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3772,13 +4574,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.434108527</v>
+        <v>0.4341085271317829</v>
       </c>
       <c r="C134" t="n">
-        <v>0.070038911</v>
+        <v>0.07003891050583658</v>
       </c>
       <c r="D134" t="n">
-        <v>0.406976744</v>
+        <v>0.4069767441860465</v>
       </c>
       <c r="E134" t="n">
         <v>14</v>
@@ -3789,6 +4591,12 @@
       <c r="G134" t="n">
         <v>17.11</v>
       </c>
+      <c r="H134" t="n">
+        <v>0.8683881759643555</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.2394164800643921</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3797,13 +4605,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.449472097</v>
+        <v>0.4494720965309201</v>
       </c>
       <c r="C135" t="n">
-        <v>0.060514372</v>
+        <v>0.06051437216338881</v>
       </c>
       <c r="D135" t="n">
-        <v>0.43438914</v>
+        <v>0.4343891402714932</v>
       </c>
       <c r="E135" t="n">
         <v>15.6</v>
@@ -3814,6 +4622,12 @@
       <c r="G135" t="n">
         <v>15.21</v>
       </c>
+      <c r="H135" t="n">
+        <v>0.8334873914718628</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.2296501845121384</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3822,10 +4636,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.425925926</v>
+        <v>0.4259259259259259</v>
       </c>
       <c r="C136" t="n">
-        <v>0.118959108</v>
+        <v>0.1189591078066914</v>
       </c>
       <c r="D136" t="n">
         <v>0.4</v>
@@ -3839,6 +4653,12 @@
       <c r="G136" t="n">
         <v>14.62</v>
       </c>
+      <c r="H136" t="n">
+        <v>0.8476560115814209</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.2424434721469879</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3847,13 +4667,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.343906511</v>
+        <v>0.343906510851419</v>
       </c>
       <c r="C137" t="n">
-        <v>0.043551089</v>
+        <v>0.04355108877721943</v>
       </c>
       <c r="D137" t="n">
-        <v>0.310517529</v>
+        <v>0.310517529215359</v>
       </c>
       <c r="E137" t="n">
         <v>14.7</v>
@@ -3864,6 +4684,12 @@
       <c r="G137" t="n">
         <v>14.74</v>
       </c>
+      <c r="H137" t="n">
+        <v>0.8346806168556213</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.2400095015764236</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3872,13 +4698,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.432569975</v>
+        <v>0.4325699745547074</v>
       </c>
       <c r="C138" t="n">
-        <v>0.112531969</v>
+        <v>0.1125319693094629</v>
       </c>
       <c r="D138" t="n">
-        <v>0.396946565</v>
+        <v>0.3969465648854961</v>
       </c>
       <c r="E138" t="n">
         <v>13.8</v>
@@ -3889,6 +4715,12 @@
       <c r="G138" t="n">
         <v>15.14</v>
       </c>
+      <c r="H138" t="n">
+        <v>0.8555185198783875</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.2462389320135117</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3897,13 +4729,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.436697248</v>
+        <v>0.436697247706422</v>
       </c>
       <c r="C139" t="n">
-        <v>0.099447514</v>
+        <v>0.09944751381215471</v>
       </c>
       <c r="D139" t="n">
-        <v>0.414678899</v>
+        <v>0.4146788990825687</v>
       </c>
       <c r="E139" t="n">
         <v>14.1</v>
@@ -3914,6 +4746,12 @@
       <c r="G139" t="n">
         <v>15.78</v>
       </c>
+      <c r="H139" t="n">
+        <v>0.8482436537742615</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.2319904118776321</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3922,13 +4760,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.338983051</v>
+        <v>0.3389830508474577</v>
       </c>
       <c r="C140" t="n">
-        <v>0.060491493</v>
+        <v>0.06049149338374291</v>
       </c>
       <c r="D140" t="n">
-        <v>0.312617702</v>
+        <v>0.312617702448211</v>
       </c>
       <c r="E140" t="n">
         <v>16.3</v>
@@ -3939,6 +4777,12 @@
       <c r="G140" t="n">
         <v>17.23</v>
       </c>
+      <c r="H140" t="n">
+        <v>0.8345646858215332</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.2376431822776794</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3947,13 +4791,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.323108384</v>
+        <v>0.3231083844580777</v>
       </c>
       <c r="C141" t="n">
-        <v>0.090349076</v>
+        <v>0.09034907597535934</v>
       </c>
       <c r="D141" t="n">
-        <v>0.306748466</v>
+        <v>0.3067484662576687</v>
       </c>
       <c r="E141" t="n">
         <v>12.6</v>
@@ -3964,6 +4808,12 @@
       <c r="G141" t="n">
         <v>14.32</v>
       </c>
+      <c r="H141" t="n">
+        <v>0.8543393015861511</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.2462163269519806</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3972,13 +4822,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.34496124</v>
+        <v>0.3449612403100776</v>
       </c>
       <c r="C142" t="n">
-        <v>0.042801556</v>
+        <v>0.04280155642023346</v>
       </c>
       <c r="D142" t="n">
-        <v>0.302325581</v>
+        <v>0.3023255813953488</v>
       </c>
       <c r="E142" t="n">
         <v>14.6</v>
@@ -3989,6 +4839,12 @@
       <c r="G142" t="n">
         <v>15.5</v>
       </c>
+      <c r="H142" t="n">
+        <v>0.8315861821174622</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.2351704686880112</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3997,13 +4853,13 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.448336252</v>
+        <v>0.4483362521891419</v>
       </c>
       <c r="C143" t="n">
-        <v>0.094903339</v>
+        <v>0.09490333919156414</v>
       </c>
       <c r="D143" t="n">
-        <v>0.409807356</v>
+        <v>0.4098073555166374</v>
       </c>
       <c r="E143" t="n">
         <v>13.9</v>
@@ -4014,6 +4870,12 @@
       <c r="G143" t="n">
         <v>13.57</v>
       </c>
+      <c r="H143" t="n">
+        <v>0.8520254492759705</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.2353335618972778</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4022,13 +4884,13 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.320137694</v>
+        <v>0.3201376936316696</v>
       </c>
       <c r="C144" t="n">
-        <v>0.06563039699999999</v>
+        <v>0.06563039723661485</v>
       </c>
       <c r="D144" t="n">
-        <v>0.296041308</v>
+        <v>0.2960413080895009</v>
       </c>
       <c r="E144" t="n">
         <v>15.2</v>
@@ -4039,6 +4901,12 @@
       <c r="G144" t="n">
         <v>16.31</v>
       </c>
+      <c r="H144" t="n">
+        <v>0.8364632129669189</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.2304713726043701</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4047,13 +4915,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.362976407</v>
+        <v>0.3629764065335753</v>
       </c>
       <c r="C145" t="n">
-        <v>0.083788707</v>
+        <v>0.08378870673952642</v>
       </c>
       <c r="D145" t="n">
-        <v>0.315789474</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="E145" t="n">
         <v>14.9</v>
@@ -4064,6 +4932,12 @@
       <c r="G145" t="n">
         <v>14.51</v>
       </c>
+      <c r="H145" t="n">
+        <v>0.8409293293952942</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.2452635765075684</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4072,13 +4946,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.455114823</v>
+        <v>0.4551148225469729</v>
       </c>
       <c r="C146" t="n">
-        <v>0.075471698</v>
+        <v>0.07547169811320754</v>
       </c>
       <c r="D146" t="n">
-        <v>0.434237996</v>
+        <v>0.4342379958246347</v>
       </c>
       <c r="E146" t="n">
         <v>13.1</v>
@@ -4089,6 +4963,12 @@
       <c r="G146" t="n">
         <v>15.32</v>
       </c>
+      <c r="H146" t="n">
+        <v>0.8509936332702637</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.2306451052427292</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4097,13 +4977,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.407619048</v>
+        <v>0.4076190476190476</v>
       </c>
       <c r="C147" t="n">
-        <v>0.061185468</v>
+        <v>0.06118546845124283</v>
       </c>
       <c r="D147" t="n">
-        <v>0.380952381</v>
+        <v>0.380952380952381</v>
       </c>
       <c r="E147" t="n">
         <v>14.5</v>
@@ -4114,6 +4994,12 @@
       <c r="G147" t="n">
         <v>16.82</v>
       </c>
+      <c r="H147" t="n">
+        <v>0.836929976940155</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.2283811122179031</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4122,13 +5008,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.395522388</v>
+        <v>0.3955223880597015</v>
       </c>
       <c r="C148" t="n">
-        <v>0.059925094</v>
+        <v>0.0599250936329588</v>
       </c>
       <c r="D148" t="n">
-        <v>0.361940299</v>
+        <v>0.3619402985074627</v>
       </c>
       <c r="E148" t="n">
         <v>12.7</v>
@@ -4139,6 +5025,12 @@
       <c r="G148" t="n">
         <v>13.23</v>
       </c>
+      <c r="H148" t="n">
+        <v>0.8431863784790039</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.2259441316127777</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4147,13 +5039,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.316498316</v>
+        <v>0.3164983164983165</v>
       </c>
       <c r="C149" t="n">
-        <v>0.057432432</v>
+        <v>0.05743243243243244</v>
       </c>
       <c r="D149" t="n">
-        <v>0.279461279</v>
+        <v>0.2794612794612795</v>
       </c>
       <c r="E149" t="n">
         <v>15.4</v>
@@ -4164,6 +5056,12 @@
       <c r="G149" t="n">
         <v>15.26</v>
       </c>
+      <c r="H149" t="n">
+        <v>0.8267980813980103</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.2236663550138474</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4172,13 +5070,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.422586521</v>
+        <v>0.4225865209471767</v>
       </c>
       <c r="C150" t="n">
-        <v>0.09140767800000001</v>
+        <v>0.09140767824497256</v>
       </c>
       <c r="D150" t="n">
-        <v>0.389799636</v>
+        <v>0.389799635701275</v>
       </c>
       <c r="E150" t="n">
         <v>15.9</v>
@@ -4189,6 +5087,12 @@
       <c r="G150" t="n">
         <v>16.95</v>
       </c>
+      <c r="H150" t="n">
+        <v>0.8460416197776794</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.2325809746980667</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4197,13 +5101,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.347504621</v>
+        <v>0.3475046210720887</v>
       </c>
       <c r="C151" t="n">
-        <v>0.09276437799999999</v>
+        <v>0.0927643784786642</v>
       </c>
       <c r="D151" t="n">
-        <v>0.31792976</v>
+        <v>0.3179297597042514</v>
       </c>
       <c r="E151" t="n">
         <v>10.5</v>
@@ -4214,6 +5118,12 @@
       <c r="G151" t="n">
         <v>10.91</v>
       </c>
+      <c r="H151" t="n">
+        <v>0.8393356204032898</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0.243650883436203</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4222,13 +5132,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.434056761</v>
+        <v>0.4340567612687813</v>
       </c>
       <c r="C152" t="n">
-        <v>0.083752094</v>
+        <v>0.08375209380234507</v>
       </c>
       <c r="D152" t="n">
-        <v>0.40066778</v>
+        <v>0.4006677796327212</v>
       </c>
       <c r="E152" t="n">
         <v>13.6</v>
@@ -4239,6 +5149,12 @@
       <c r="G152" t="n">
         <v>14.86</v>
       </c>
+      <c r="H152" t="n">
+        <v>0.8369390964508057</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0.2306000590324402</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4247,13 +5163,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.506876228</v>
+        <v>0.5068762278978389</v>
       </c>
       <c r="C153" t="n">
-        <v>0.17357002</v>
+        <v>0.1735700197238659</v>
       </c>
       <c r="D153" t="n">
-        <v>0.479371316</v>
+        <v>0.4793713163064833</v>
       </c>
       <c r="E153" t="n">
         <v>13.6</v>
@@ -4264,6 +5180,12 @@
       <c r="G153" t="n">
         <v>14.56</v>
       </c>
+      <c r="H153" t="n">
+        <v>0.8597341775894165</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.2254450470209122</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4272,13 +5194,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.374291115</v>
+        <v>0.3742911153119093</v>
       </c>
       <c r="C154" t="n">
-        <v>0.110056926</v>
+        <v>0.1100569259962049</v>
       </c>
       <c r="D154" t="n">
-        <v>0.34026465</v>
+        <v>0.3402646502835539</v>
       </c>
       <c r="E154" t="n">
         <v>14.5</v>
@@ -4289,6 +5211,12 @@
       <c r="G154" t="n">
         <v>15.38</v>
       </c>
+      <c r="H154" t="n">
+        <v>0.8439069390296936</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.2313440293073654</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4297,13 +5225,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.414784394</v>
+        <v>0.4147843942505133</v>
       </c>
       <c r="C155" t="n">
-        <v>0.09896907200000001</v>
+        <v>0.09896907216494846</v>
       </c>
       <c r="D155" t="n">
-        <v>0.394250513</v>
+        <v>0.3942505133470226</v>
       </c>
       <c r="E155" t="n">
         <v>14.9</v>
@@ -4314,6 +5242,12 @@
       <c r="G155" t="n">
         <v>15.26</v>
       </c>
+      <c r="H155" t="n">
+        <v>0.844812273979187</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.2323092520236969</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4322,13 +5256,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.372649573</v>
+        <v>0.3726495726495726</v>
       </c>
       <c r="C156" t="n">
-        <v>0.024013722</v>
+        <v>0.02401372212692967</v>
       </c>
       <c r="D156" t="n">
-        <v>0.355555556</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="E156" t="n">
         <v>15.2</v>
@@ -4339,6 +5273,12 @@
       <c r="G156" t="n">
         <v>15.21</v>
       </c>
+      <c r="H156" t="n">
+        <v>0.8254528641700745</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.2310575544834137</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4347,13 +5287,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.362886598</v>
+        <v>0.3628865979381443</v>
       </c>
       <c r="C157" t="n">
-        <v>0.074534161</v>
+        <v>0.07453416149068325</v>
       </c>
       <c r="D157" t="n">
-        <v>0.334020619</v>
+        <v>0.334020618556701</v>
       </c>
       <c r="E157" t="n">
         <v>13.7</v>
@@ -4364,6 +5304,12 @@
       <c r="G157" t="n">
         <v>16.24</v>
       </c>
+      <c r="H157" t="n">
+        <v>0.8469189405441284</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.2461041659116745</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4372,13 +5318,13 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.391472868</v>
+        <v>0.3914728682170543</v>
       </c>
       <c r="C158" t="n">
-        <v>0.070038911</v>
+        <v>0.07003891050583658</v>
       </c>
       <c r="D158" t="n">
-        <v>0.325581395</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="E158" t="n">
         <v>14.6</v>
@@ -4389,6 +5335,12 @@
       <c r="G158" t="n">
         <v>14.51</v>
       </c>
+      <c r="H158" t="n">
+        <v>0.8461540937423706</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.2334669828414917</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4397,13 +5349,13 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.33968254</v>
+        <v>0.3396825396825396</v>
       </c>
       <c r="C159" t="n">
-        <v>0.070063694</v>
+        <v>0.07006369426751592</v>
       </c>
       <c r="D159" t="n">
-        <v>0.304761905</v>
+        <v>0.3047619047619047</v>
       </c>
       <c r="E159" t="n">
         <v>13.6</v>
@@ -4414,6 +5366,12 @@
       <c r="G159" t="n">
         <v>16.13</v>
       </c>
+      <c r="H159" t="n">
+        <v>0.8295682668685913</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0.2406269311904907</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4422,13 +5380,13 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.375838926</v>
+        <v>0.3758389261744966</v>
       </c>
       <c r="C160" t="n">
-        <v>0.097643098</v>
+        <v>0.09764309764309764</v>
       </c>
       <c r="D160" t="n">
-        <v>0.352348993</v>
+        <v>0.3523489932885907</v>
       </c>
       <c r="E160" t="n">
         <v>12</v>
@@ -4439,6 +5397,12 @@
       <c r="G160" t="n">
         <v>12.59</v>
       </c>
+      <c r="H160" t="n">
+        <v>0.847368597984314</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.2365166693925858</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4447,13 +5411,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.294820717</v>
+        <v>0.2948207171314741</v>
       </c>
       <c r="C161" t="n">
-        <v>0.056</v>
+        <v>0.05600000000000001</v>
       </c>
       <c r="D161" t="n">
-        <v>0.274900398</v>
+        <v>0.2749003984063745</v>
       </c>
       <c r="E161" t="n">
         <v>16</v>
@@ -4464,6 +5428,12 @@
       <c r="G161" t="n">
         <v>16.48</v>
       </c>
+      <c r="H161" t="n">
+        <v>0.8457242250442505</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.2709794938564301</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4472,13 +5442,13 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.36329588</v>
+        <v>0.3632958801498128</v>
       </c>
       <c r="C162" t="n">
-        <v>0.09398496200000001</v>
+        <v>0.09398496240601503</v>
       </c>
       <c r="D162" t="n">
-        <v>0.348314607</v>
+        <v>0.3483146067415731</v>
       </c>
       <c r="E162" t="n">
         <v>13.6</v>
@@ -4489,6 +5459,12 @@
       <c r="G162" t="n">
         <v>16.13</v>
       </c>
+      <c r="H162" t="n">
+        <v>0.8467015027999878</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.234626904129982</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4497,13 +5473,13 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.426229508</v>
+        <v>0.4262295081967213</v>
       </c>
       <c r="C163" t="n">
-        <v>0.089411765</v>
+        <v>0.08941176470588234</v>
       </c>
       <c r="D163" t="n">
-        <v>0.393442623</v>
+        <v>0.3934426229508196</v>
       </c>
       <c r="E163" t="n">
         <v>16.5</v>
@@ -4514,6 +5490,12 @@
       <c r="G163" t="n">
         <v>16.95</v>
       </c>
+      <c r="H163" t="n">
+        <v>0.8628225326538086</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.2250519543886185</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4522,13 +5504,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.397260274</v>
+        <v>0.3972602739726027</v>
       </c>
       <c r="C164" t="n">
-        <v>0.133027523</v>
+        <v>0.1330275229357798</v>
       </c>
       <c r="D164" t="n">
-        <v>0.378995434</v>
+        <v>0.3789954337899544</v>
       </c>
       <c r="E164" t="n">
         <v>12.4</v>
@@ -4539,6 +5521,12 @@
       <c r="G164" t="n">
         <v>14.45</v>
       </c>
+      <c r="H164" t="n">
+        <v>0.8550536632537842</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.2471037656068802</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4547,13 +5535,13 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.393333333</v>
+        <v>0.3933333333333333</v>
       </c>
       <c r="C165" t="n">
-        <v>0.117056856</v>
+        <v>0.117056856187291</v>
       </c>
       <c r="D165" t="n">
-        <v>0.373333333</v>
+        <v>0.3733333333333334</v>
       </c>
       <c r="E165" t="n">
         <v>14</v>
@@ -4564,6 +5552,12 @@
       <c r="G165" t="n">
         <v>14.22</v>
       </c>
+      <c r="H165" t="n">
+        <v>0.8388577103614807</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.2343595921993256</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4572,13 +5566,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.371475954</v>
+        <v>0.3714759535655058</v>
       </c>
       <c r="C166" t="n">
-        <v>0.06655574</v>
+        <v>0.06655574043261232</v>
       </c>
       <c r="D166" t="n">
-        <v>0.341625207</v>
+        <v>0.341625207296849</v>
       </c>
       <c r="E166" t="n">
         <v>12.6</v>
@@ -4589,6 +5583,12 @@
       <c r="G166" t="n">
         <v>15.43</v>
       </c>
+      <c r="H166" t="n">
+        <v>0.8319783210754395</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0.2341125905513763</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4597,13 +5597,13 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.495956873</v>
+        <v>0.4959568733153639</v>
       </c>
       <c r="C167" t="n">
-        <v>0.124661247</v>
+        <v>0.1246612466124661</v>
       </c>
       <c r="D167" t="n">
-        <v>0.46361186</v>
+        <v>0.463611859838275</v>
       </c>
       <c r="E167" t="n">
         <v>13.2</v>
@@ -4614,6 +5614,12 @@
       <c r="G167" t="n">
         <v>14.22</v>
       </c>
+      <c r="H167" t="n">
+        <v>0.8638114929199219</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0.2213018089532852</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4622,13 +5628,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.501216545</v>
+        <v>0.5012165450121654</v>
       </c>
       <c r="C168" t="n">
-        <v>0.171149144</v>
+        <v>0.1711491442542787</v>
       </c>
       <c r="D168" t="n">
-        <v>0.481751825</v>
+        <v>0.4817518248175183</v>
       </c>
       <c r="E168" t="n">
         <v>11.9</v>
@@ -4639,6 +5645,12 @@
       <c r="G168" t="n">
         <v>13.4</v>
       </c>
+      <c r="H168" t="n">
+        <v>0.8679723739624023</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0.2362310737371445</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4647,13 +5659,13 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.414893617</v>
+        <v>0.4148936170212766</v>
       </c>
       <c r="C169" t="n">
-        <v>0.078291815</v>
+        <v>0.07829181494661921</v>
       </c>
       <c r="D169" t="n">
-        <v>0.386524823</v>
+        <v>0.3865248226950354</v>
       </c>
       <c r="E169" t="n">
         <v>12.1</v>
@@ -4664,6 +5676,12 @@
       <c r="G169" t="n">
         <v>13.81</v>
       </c>
+      <c r="H169" t="n">
+        <v>0.8470199108123779</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0.2336343675851822</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4672,13 +5690,13 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.465116279</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="C170" t="n">
-        <v>0.176666667</v>
+        <v>0.1766666666666667</v>
       </c>
       <c r="D170" t="n">
-        <v>0.438538206</v>
+        <v>0.4385382059800665</v>
       </c>
       <c r="E170" t="n">
         <v>11</v>
@@ -4689,6 +5707,12 @@
       <c r="G170" t="n">
         <v>13.34</v>
       </c>
+      <c r="H170" t="n">
+        <v>0.8695294857025146</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0.2599412202835083</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4697,13 +5721,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.363247863</v>
+        <v>0.3632478632478632</v>
       </c>
       <c r="C171" t="n">
-        <v>0.06866952799999999</v>
+        <v>0.06866952789699571</v>
       </c>
       <c r="D171" t="n">
-        <v>0.346153846</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="E171" t="n">
         <v>12.1</v>
@@ -4714,6 +5738,12 @@
       <c r="G171" t="n">
         <v>14.27</v>
       </c>
+      <c r="H171" t="n">
+        <v>0.8385193347930908</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0.2335834056138992</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4722,13 +5752,13 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.359848485</v>
+        <v>0.3598484848484849</v>
       </c>
       <c r="C172" t="n">
-        <v>0.068441065</v>
+        <v>0.06844106463878327</v>
       </c>
       <c r="D172" t="n">
-        <v>0.318181818</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="E172" t="n">
         <v>14.8</v>
@@ -4739,6 +5769,12 @@
       <c r="G172" t="n">
         <v>16.82</v>
       </c>
+      <c r="H172" t="n">
+        <v>0.8351394534111023</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0.2319751083850861</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4747,13 +5783,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.349907919</v>
+        <v>0.3499079189686925</v>
       </c>
       <c r="C173" t="n">
-        <v>0.096118299</v>
+        <v>0.09611829944547134</v>
       </c>
       <c r="D173" t="n">
-        <v>0.305709024</v>
+        <v>0.3057090239410682</v>
       </c>
       <c r="E173" t="n">
         <v>14.2</v>
@@ -4764,6 +5800,12 @@
       <c r="G173" t="n">
         <v>15.37</v>
       </c>
+      <c r="H173" t="n">
+        <v>0.8332948088645935</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.2397510707378387</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4772,13 +5814,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.431118314</v>
+        <v>0.4311183144246353</v>
       </c>
       <c r="C174" t="n">
-        <v>0.09430894300000001</v>
+        <v>0.0943089430894309</v>
       </c>
       <c r="D174" t="n">
-        <v>0.405186386</v>
+        <v>0.4051863857374393</v>
       </c>
       <c r="E174" t="n">
         <v>13.5</v>
@@ -4789,6 +5831,12 @@
       <c r="G174" t="n">
         <v>16.13</v>
       </c>
+      <c r="H174" t="n">
+        <v>0.8406352400779724</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0.2358406186103821</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4797,13 +5845,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.356687898</v>
+        <v>0.356687898089172</v>
       </c>
       <c r="C175" t="n">
-        <v>0.076759062</v>
+        <v>0.07675906183368869</v>
       </c>
       <c r="D175" t="n">
-        <v>0.322717622</v>
+        <v>0.3227176220806794</v>
       </c>
       <c r="E175" t="n">
         <v>16.5</v>
@@ -4814,6 +5862,12 @@
       <c r="G175" t="n">
         <v>19.26</v>
       </c>
+      <c r="H175" t="n">
+        <v>0.8439502120018005</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0.2233222424983978</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4822,13 +5876,13 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.405109489</v>
+        <v>0.4051094890510949</v>
       </c>
       <c r="C176" t="n">
-        <v>0.106227106</v>
+        <v>0.1062271062271062</v>
       </c>
       <c r="D176" t="n">
-        <v>0.390510949</v>
+        <v>0.3905109489051095</v>
       </c>
       <c r="E176" t="n">
         <v>14.5</v>
@@ -4839,6 +5893,12 @@
       <c r="G176" t="n">
         <v>16.59</v>
       </c>
+      <c r="H176" t="n">
+        <v>0.8482267260551453</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0.2345162481069565</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4847,13 +5907,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.4238921</v>
+        <v>0.4238921001926783</v>
       </c>
       <c r="C177" t="n">
-        <v>0.08897485500000001</v>
+        <v>0.08897485493230174</v>
       </c>
       <c r="D177" t="n">
-        <v>0.38150289</v>
+        <v>0.3815028901734104</v>
       </c>
       <c r="E177" t="n">
         <v>13.8</v>
@@ -4864,6 +5924,12 @@
       <c r="G177" t="n">
         <v>15.37</v>
       </c>
+      <c r="H177" t="n">
+        <v>0.8427902460098267</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0.2347385287284851</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4872,13 +5938,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.346349745</v>
+        <v>0.3463497453310697</v>
       </c>
       <c r="C178" t="n">
-        <v>0.08177172100000001</v>
+        <v>0.0817717206132879</v>
       </c>
       <c r="D178" t="n">
-        <v>0.322580645</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="E178" t="n">
         <v>14.5</v>
@@ -4889,6 +5955,12 @@
       <c r="G178" t="n">
         <v>16.37</v>
       </c>
+      <c r="H178" t="n">
+        <v>0.8342552185058594</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0.2280473262071609</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4897,13 +5969,13 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.379928315</v>
+        <v>0.3799283154121864</v>
       </c>
       <c r="C179" t="n">
-        <v>0.086330935</v>
+        <v>0.08633093525179857</v>
       </c>
       <c r="D179" t="n">
-        <v>0.35483871</v>
+        <v>0.3548387096774193</v>
       </c>
       <c r="E179" t="n">
         <v>13.9</v>
@@ -4914,6 +5986,12 @@
       <c r="G179" t="n">
         <v>14.16</v>
       </c>
+      <c r="H179" t="n">
+        <v>0.838157057762146</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0.2282051891088486</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4922,13 +6000,13 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.391930836</v>
+        <v>0.3919308357348704</v>
       </c>
       <c r="C180" t="n">
-        <v>0.063768116</v>
+        <v>0.063768115942029</v>
       </c>
       <c r="D180" t="n">
-        <v>0.368876081</v>
+        <v>0.3688760806916427</v>
       </c>
       <c r="E180" t="n">
         <v>16.3</v>
@@ -4939,6 +6017,12 @@
       <c r="G180" t="n">
         <v>17.58</v>
       </c>
+      <c r="H180" t="n">
+        <v>0.8517221212387085</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0.2151313424110413</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4947,13 +6031,13 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.485943775</v>
+        <v>0.4859437751004016</v>
       </c>
       <c r="C181" t="n">
-        <v>0.09677419399999999</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="D181" t="n">
-        <v>0.445783133</v>
+        <v>0.4457831325301205</v>
       </c>
       <c r="E181" t="n">
         <v>16.5</v>
@@ -4964,6 +6048,12 @@
       <c r="G181" t="n">
         <v>16.37</v>
       </c>
+      <c r="H181" t="n">
+        <v>0.8490369915962219</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0.2335629612207413</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4972,13 +6062,13 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.338762215</v>
+        <v>0.3387622149837133</v>
       </c>
       <c r="C182" t="n">
-        <v>0.08169934600000001</v>
+        <v>0.08169934640522875</v>
       </c>
       <c r="D182" t="n">
-        <v>0.312703583</v>
+        <v>0.3127035830618892</v>
       </c>
       <c r="E182" t="n">
         <v>13.3</v>
@@ -4989,6 +6079,12 @@
       <c r="G182" t="n">
         <v>14.85</v>
       </c>
+      <c r="H182" t="n">
+        <v>0.8290675282478333</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0.2432645261287689</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4997,13 +6093,13 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C183" t="n">
-        <v>0.07042253499999999</v>
+        <v>0.07042253521126761</v>
       </c>
       <c r="D183" t="n">
-        <v>0.294736842</v>
+        <v>0.2947368421052631</v>
       </c>
       <c r="E183" t="n">
         <v>14.7</v>
@@ -5014,6 +6110,12 @@
       <c r="G183" t="n">
         <v>16.19</v>
       </c>
+      <c r="H183" t="n">
+        <v>0.8453928232192993</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0.2357201725244522</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5022,13 +6124,13 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.387858347</v>
+        <v>0.387858347386172</v>
       </c>
       <c r="C184" t="n">
-        <v>0.08121827399999999</v>
+        <v>0.08121827411167512</v>
       </c>
       <c r="D184" t="n">
-        <v>0.354131535</v>
+        <v>0.3541315345699831</v>
       </c>
       <c r="E184" t="n">
         <v>14.4</v>
@@ -5039,6 +6141,12 @@
       <c r="G184" t="n">
         <v>14.57</v>
       </c>
+      <c r="H184" t="n">
+        <v>0.8410611748695374</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0.2303756177425385</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5047,13 +6155,13 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.507337526</v>
+        <v>0.5073375262054507</v>
       </c>
       <c r="C185" t="n">
-        <v>0.122105263</v>
+        <v>0.1221052631578947</v>
       </c>
       <c r="D185" t="n">
-        <v>0.486373166</v>
+        <v>0.4863731656184487</v>
       </c>
       <c r="E185" t="n">
         <v>11.7</v>
@@ -5064,6 +6172,12 @@
       <c r="G185" t="n">
         <v>13.52</v>
       </c>
+      <c r="H185" t="n">
+        <v>0.8498260378837585</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0.2309439331293106</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5072,13 +6186,13 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.503198294</v>
+        <v>0.5031982942430703</v>
       </c>
       <c r="C186" t="n">
-        <v>0.107066381</v>
+        <v>0.1070663811563169</v>
       </c>
       <c r="D186" t="n">
-        <v>0.481876333</v>
+        <v>0.4818763326226013</v>
       </c>
       <c r="E186" t="n">
         <v>12.4</v>
@@ -5089,6 +6203,12 @@
       <c r="G186" t="n">
         <v>12.59</v>
       </c>
+      <c r="H186" t="n">
+        <v>0.8576430678367615</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0.2447107881307602</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5097,13 +6217,13 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.445396146</v>
+        <v>0.4453961456102784</v>
       </c>
       <c r="C187" t="n">
-        <v>0.098924731</v>
+        <v>0.0989247311827957</v>
       </c>
       <c r="D187" t="n">
-        <v>0.419700214</v>
+        <v>0.4197002141327623</v>
       </c>
       <c r="E187" t="n">
         <v>16.6</v>
@@ -5114,6 +6234,12 @@
       <c r="G187" t="n">
         <v>17.11</v>
       </c>
+      <c r="H187" t="n">
+        <v>0.8618149161338806</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0.2215899974107742</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5122,13 +6248,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.474264706</v>
+        <v>0.474264705882353</v>
       </c>
       <c r="C188" t="n">
-        <v>0.147601476</v>
+        <v>0.1476014760147601</v>
       </c>
       <c r="D188" t="n">
-        <v>0.430147059</v>
+        <v>0.4301470588235294</v>
       </c>
       <c r="E188" t="n">
         <v>15.5</v>
@@ -5139,6 +6265,12 @@
       <c r="G188" t="n">
         <v>13.87</v>
       </c>
+      <c r="H188" t="n">
+        <v>0.8489512205123901</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0.2193189412355423</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5147,13 +6279,13 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.448484848</v>
+        <v>0.4484848484848485</v>
       </c>
       <c r="C189" t="n">
-        <v>0.113590264</v>
+        <v>0.1135902636916836</v>
       </c>
       <c r="D189" t="n">
-        <v>0.412121212</v>
+        <v>0.4121212121212121</v>
       </c>
       <c r="E189" t="n">
         <v>12.7</v>
@@ -5164,6 +6296,12 @@
       <c r="G189" t="n">
         <v>12.13</v>
       </c>
+      <c r="H189" t="n">
+        <v>0.8497258424758911</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.224247932434082</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5172,13 +6310,13 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.452504318</v>
+        <v>0.4525043177892919</v>
       </c>
       <c r="C190" t="n">
-        <v>0.128249567</v>
+        <v>0.1282495667244367</v>
       </c>
       <c r="D190" t="n">
-        <v>0.424870466</v>
+        <v>0.4248704663212436</v>
       </c>
       <c r="E190" t="n">
         <v>15.7</v>
@@ -5189,6 +6327,12 @@
       <c r="G190" t="n">
         <v>17.35</v>
       </c>
+      <c r="H190" t="n">
+        <v>0.8501020073890686</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.2299175709486008</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5197,13 +6341,13 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.429090909</v>
+        <v>0.4290909090909091</v>
       </c>
       <c r="C191" t="n">
-        <v>0.124087591</v>
+        <v>0.1240875912408759</v>
       </c>
       <c r="D191" t="n">
-        <v>0.392727273</v>
+        <v>0.3927272727272727</v>
       </c>
       <c r="E191" t="n">
         <v>12.5</v>
@@ -5214,6 +6358,12 @@
       <c r="G191" t="n">
         <v>13.52</v>
       </c>
+      <c r="H191" t="n">
+        <v>0.8455148935317993</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0.2233232259750366</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5222,13 +6372,13 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.340681363</v>
+        <v>0.3406813627254509</v>
       </c>
       <c r="C192" t="n">
-        <v>0.068410463</v>
+        <v>0.06841046277665995</v>
       </c>
       <c r="D192" t="n">
-        <v>0.320641283</v>
+        <v>0.3206412825651303</v>
       </c>
       <c r="E192" t="n">
         <v>12.4</v>
@@ -5239,6 +6389,12 @@
       <c r="G192" t="n">
         <v>15.55</v>
       </c>
+      <c r="H192" t="n">
+        <v>0.849726140499115</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0.2323938757181168</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5247,13 +6403,13 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.498194946</v>
+        <v>0.4981949458483755</v>
       </c>
       <c r="C193" t="n">
-        <v>0.101449275</v>
+        <v>0.1014492753623188</v>
       </c>
       <c r="D193" t="n">
-        <v>0.454873646</v>
+        <v>0.4548736462093863</v>
       </c>
       <c r="E193" t="n">
         <v>14.6</v>
@@ -5264,6 +6420,12 @@
       <c r="G193" t="n">
         <v>14.8</v>
       </c>
+      <c r="H193" t="n">
+        <v>0.8458873629570007</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0.224018931388855</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5272,13 +6434,13 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.3728223</v>
+        <v>0.3728222996515679</v>
       </c>
       <c r="C194" t="n">
-        <v>0.066433566</v>
+        <v>0.06643356643356643</v>
       </c>
       <c r="D194" t="n">
-        <v>0.348432056</v>
+        <v>0.3484320557491289</v>
       </c>
       <c r="E194" t="n">
         <v>15.2</v>
@@ -5289,6 +6451,12 @@
       <c r="G194" t="n">
         <v>17.52</v>
       </c>
+      <c r="H194" t="n">
+        <v>0.8359677195549011</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0.2314401417970657</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5297,13 +6465,13 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.409090909</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="C195" t="n">
-        <v>0.053941909</v>
+        <v>0.05394190871369295</v>
       </c>
       <c r="D195" t="n">
-        <v>0.376033058</v>
+        <v>0.3760330578512397</v>
       </c>
       <c r="E195" t="n">
         <v>15.7</v>
@@ -5314,6 +6482,12 @@
       <c r="G195" t="n">
         <v>17.4</v>
       </c>
+      <c r="H195" t="n">
+        <v>0.8432568311691284</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0.2296909540891647</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5322,13 +6496,13 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.415026834</v>
+        <v>0.4150268336314848</v>
       </c>
       <c r="C196" t="n">
-        <v>0.078994614</v>
+        <v>0.07899461400359066</v>
       </c>
       <c r="D196" t="n">
-        <v>0.386404293</v>
+        <v>0.3864042933810376</v>
       </c>
       <c r="E196" t="n">
         <v>17</v>
@@ -5339,6 +6513,12 @@
       <c r="G196" t="n">
         <v>17.06</v>
       </c>
+      <c r="H196" t="n">
+        <v>0.838357150554657</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0.2262725383043289</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5347,13 +6527,13 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.536290323</v>
+        <v>0.5362903225806451</v>
       </c>
       <c r="C197" t="n">
-        <v>0.153846154</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="D197" t="n">
-        <v>0.487903226</v>
+        <v>0.4879032258064517</v>
       </c>
       <c r="E197" t="n">
         <v>15.2</v>
@@ -5364,6 +6544,12 @@
       <c r="G197" t="n">
         <v>14.57</v>
       </c>
+      <c r="H197" t="n">
+        <v>0.8560428619384766</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0.2283775508403778</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5372,13 +6558,13 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.437086093</v>
+        <v>0.4370860927152318</v>
       </c>
       <c r="C198" t="n">
-        <v>0.093023256</v>
+        <v>0.09302325581395349</v>
       </c>
       <c r="D198" t="n">
-        <v>0.410596026</v>
+        <v>0.4105960264900662</v>
       </c>
       <c r="E198" t="n">
         <v>12.3</v>
@@ -5389,6 +6575,12 @@
       <c r="G198" t="n">
         <v>13.17</v>
       </c>
+      <c r="H198" t="n">
+        <v>0.8389963507652283</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0.2471075505018234</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5397,13 +6589,13 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.506517691</v>
+        <v>0.5065176908752328</v>
       </c>
       <c r="C199" t="n">
-        <v>0.078504673</v>
+        <v>0.07850467289719626</v>
       </c>
       <c r="D199" t="n">
-        <v>0.487895717</v>
+        <v>0.4878957169459963</v>
       </c>
       <c r="E199" t="n">
         <v>15.7</v>
@@ -5414,6 +6606,12 @@
       <c r="G199" t="n">
         <v>17.52</v>
       </c>
+      <c r="H199" t="n">
+        <v>0.8490070700645447</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0.2267344892024994</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5422,13 +6620,13 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.476584022</v>
+        <v>0.4765840220385676</v>
       </c>
       <c r="C200" t="n">
-        <v>0.140883978</v>
+        <v>0.1408839779005525</v>
       </c>
       <c r="D200" t="n">
-        <v>0.454545455</v>
+        <v>0.4545454545454546</v>
       </c>
       <c r="E200" t="n">
         <v>10.9</v>
@@ -5439,6 +6637,12 @@
       <c r="G200" t="n">
         <v>11.66</v>
       </c>
+      <c r="H200" t="n">
+        <v>0.8400211334228516</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0.2370614111423492</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5447,13 +6651,13 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.498327759</v>
+        <v>0.4983277591973245</v>
       </c>
       <c r="C201" t="n">
-        <v>0.087248322</v>
+        <v>0.08724832214765101</v>
       </c>
       <c r="D201" t="n">
-        <v>0.474916388</v>
+        <v>0.4749163879598662</v>
       </c>
       <c r="E201" t="n">
         <v>12.1</v>
@@ -5464,6 +6668,12 @@
       <c r="G201" t="n">
         <v>13.81</v>
       </c>
+      <c r="H201" t="n">
+        <v>0.8524822592735291</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0.2444892823696136</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5472,13 +6682,13 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.372623574</v>
+        <v>0.3726235741444867</v>
       </c>
       <c r="C202" t="n">
-        <v>0.06870229</v>
+        <v>0.06870229007633587</v>
       </c>
       <c r="D202" t="n">
-        <v>0.349809886</v>
+        <v>0.3498098859315589</v>
       </c>
       <c r="E202" t="n">
         <v>17.9</v>
@@ -5489,6 +6699,12 @@
       <c r="G202" t="n">
         <v>16.42</v>
       </c>
+      <c r="H202" t="n">
+        <v>0.8442518711090088</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0.2226542532444</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5497,13 +6713,13 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.494577007</v>
+        <v>0.4945770065075922</v>
       </c>
       <c r="C203" t="n">
-        <v>0.148148148</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="D203" t="n">
-        <v>0.442516269</v>
+        <v>0.4425162689804772</v>
       </c>
       <c r="E203" t="n">
         <v>12.8</v>
@@ -5514,6 +6730,12 @@
       <c r="G203" t="n">
         <v>14.27</v>
       </c>
+      <c r="H203" t="n">
+        <v>0.87091064453125</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0.2512629926204681</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5522,13 +6744,13 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.470355731</v>
+        <v>0.4703557312252964</v>
       </c>
       <c r="C204" t="n">
-        <v>0.07936507900000001</v>
+        <v>0.07936507936507937</v>
       </c>
       <c r="D204" t="n">
-        <v>0.43083004</v>
+        <v>0.4308300395256918</v>
       </c>
       <c r="E204" t="n">
         <v>13.5</v>
@@ -5539,6 +6761,12 @@
       <c r="G204" t="n">
         <v>15.78</v>
       </c>
+      <c r="H204" t="n">
+        <v>0.8434149026870728</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0.2281105816364288</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5547,13 +6775,13 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.361788618</v>
+        <v>0.3617886178861788</v>
       </c>
       <c r="C205" t="n">
-        <v>0.07755102</v>
+        <v>0.07755102040816327</v>
       </c>
       <c r="D205" t="n">
-        <v>0.345528455</v>
+        <v>0.3455284552845528</v>
       </c>
       <c r="E205" t="n">
         <v>15.7</v>
@@ -5564,6 +6792,12 @@
       <c r="G205" t="n">
         <v>15.95</v>
       </c>
+      <c r="H205" t="n">
+        <v>0.8403315544128418</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0.2239806801080704</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5572,13 +6806,13 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.363636364</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="C206" t="n">
-        <v>0.048192771</v>
+        <v>0.04819277108433734</v>
       </c>
       <c r="D206" t="n">
-        <v>0.319039451</v>
+        <v>0.3190394511149228</v>
       </c>
       <c r="E206" t="n">
         <v>14.4</v>
@@ -5589,6 +6823,12 @@
       <c r="G206" t="n">
         <v>15.61</v>
       </c>
+      <c r="H206" t="n">
+        <v>0.8315596580505371</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0.2412226349115372</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5597,13 +6837,13 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.32172471</v>
+        <v>0.3217247097844112</v>
       </c>
       <c r="C207" t="n">
-        <v>0.056572379</v>
+        <v>0.05657237936772046</v>
       </c>
       <c r="D207" t="n">
-        <v>0.305140962</v>
+        <v>0.3051409618573797</v>
       </c>
       <c r="E207" t="n">
         <v>16.4</v>
@@ -5614,6 +6854,12 @@
       <c r="G207" t="n">
         <v>16.82</v>
       </c>
+      <c r="H207" t="n">
+        <v>0.8348941206932068</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0.2417695075273514</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5622,13 +6868,13 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.424354244</v>
+        <v>0.4243542435424354</v>
       </c>
       <c r="C208" t="n">
-        <v>0.114814815</v>
+        <v>0.1148148148148148</v>
       </c>
       <c r="D208" t="n">
-        <v>0.398523985</v>
+        <v>0.3985239852398524</v>
       </c>
       <c r="E208" t="n">
         <v>16.4</v>
@@ -5639,6 +6885,12 @@
       <c r="G208" t="n">
         <v>17.35</v>
       </c>
+      <c r="H208" t="n">
+        <v>0.8550693988800049</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0.2451402395963669</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5647,13 +6899,13 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.404347826</v>
+        <v>0.4043478260869566</v>
       </c>
       <c r="C209" t="n">
-        <v>0.074235808</v>
+        <v>0.074235807860262</v>
       </c>
       <c r="D209" t="n">
-        <v>0.373913043</v>
+        <v>0.3739130434782609</v>
       </c>
       <c r="E209" t="n">
         <v>18.7</v>
@@ -5664,6 +6916,12 @@
       <c r="G209" t="n">
         <v>17.76</v>
       </c>
+      <c r="H209" t="n">
+        <v>0.8480873107910156</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0.2231202721595764</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5672,13 +6930,13 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.357758621</v>
+        <v>0.3577586206896551</v>
       </c>
       <c r="C210" t="n">
-        <v>0.086580087</v>
+        <v>0.08658008658008658</v>
       </c>
       <c r="D210" t="n">
-        <v>0.318965517</v>
+        <v>0.3189655172413793</v>
       </c>
       <c r="E210" t="n">
         <v>16.3</v>
@@ -5689,6 +6947,12 @@
       <c r="G210" t="n">
         <v>18.51</v>
       </c>
+      <c r="H210" t="n">
+        <v>0.842330276966095</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0.2372325509786606</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5697,13 +6961,13 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.463465553</v>
+        <v>0.4634655532359082</v>
       </c>
       <c r="C211" t="n">
-        <v>0.134171908</v>
+        <v>0.1341719077568134</v>
       </c>
       <c r="D211" t="n">
-        <v>0.409185804</v>
+        <v>0.4091858037578288</v>
       </c>
       <c r="E211" t="n">
         <v>15.4</v>
@@ -5714,6 +6978,12 @@
       <c r="G211" t="n">
         <v>14.68</v>
       </c>
+      <c r="H211" t="n">
+        <v>0.8532179594039917</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0.223759651184082</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5722,13 +6992,13 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.494845361</v>
+        <v>0.4948453608247423</v>
       </c>
       <c r="C212" t="n">
-        <v>0.131034483</v>
+        <v>0.1310344827586207</v>
       </c>
       <c r="D212" t="n">
-        <v>0.474226804</v>
+        <v>0.4742268041237113</v>
       </c>
       <c r="E212" t="n">
         <v>15</v>
@@ -5739,6 +7009,12 @@
       <c r="G212" t="n">
         <v>16.82</v>
       </c>
+      <c r="H212" t="n">
+        <v>0.8526734709739685</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0.226719856262207</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5747,13 +7023,13 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.390151515</v>
+        <v>0.3901515151515151</v>
       </c>
       <c r="C213" t="n">
-        <v>0.098859316</v>
+        <v>0.09885931558935361</v>
       </c>
       <c r="D213" t="n">
-        <v>0.367424242</v>
+        <v>0.3674242424242424</v>
       </c>
       <c r="E213" t="n">
         <v>17.7</v>
@@ -5764,6 +7040,12 @@
       <c r="G213" t="n">
         <v>18.28</v>
       </c>
+      <c r="H213" t="n">
+        <v>0.8416885137557983</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.2335358560085297</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5772,13 +7054,13 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.424561404</v>
+        <v>0.4245614035087719</v>
       </c>
       <c r="C214" t="n">
-        <v>0.10915493</v>
+        <v>0.1091549295774648</v>
       </c>
       <c r="D214" t="n">
-        <v>0.392982456</v>
+        <v>0.3929824561403509</v>
       </c>
       <c r="E214" t="n">
         <v>13.6</v>
@@ -5789,6 +7071,12 @@
       <c r="G214" t="n">
         <v>15.84</v>
       </c>
+      <c r="H214" t="n">
+        <v>0.8566688299179077</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0.241594135761261</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5797,13 +7085,13 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.385288967</v>
+        <v>0.3852889667250439</v>
       </c>
       <c r="C215" t="n">
-        <v>0.059753954</v>
+        <v>0.05975395430579964</v>
       </c>
       <c r="D215" t="n">
-        <v>0.367775832</v>
+        <v>0.3677758318739055</v>
       </c>
       <c r="E215" t="n">
         <v>12.2</v>
@@ -5814,6 +7102,12 @@
       <c r="G215" t="n">
         <v>14.04</v>
       </c>
+      <c r="H215" t="n">
+        <v>0.8394346833229065</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0.251975029706955</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5822,13 +7116,13 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.354898336</v>
+        <v>0.3548983364140481</v>
       </c>
       <c r="C216" t="n">
-        <v>0.09276437799999999</v>
+        <v>0.09276437847866419</v>
       </c>
       <c r="D216" t="n">
-        <v>0.329020333</v>
+        <v>0.3290203327171904</v>
       </c>
       <c r="E216" t="n">
         <v>14.1</v>
@@ -5839,6 +7133,12 @@
       <c r="G216" t="n">
         <v>15.55</v>
       </c>
+      <c r="H216" t="n">
+        <v>0.8495108485221863</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0.2313159257173538</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5847,13 +7147,13 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.363001745</v>
+        <v>0.363001745200698</v>
       </c>
       <c r="C217" t="n">
-        <v>0.108581436</v>
+        <v>0.1085814360770578</v>
       </c>
       <c r="D217" t="n">
-        <v>0.335078534</v>
+        <v>0.3350785340314136</v>
       </c>
       <c r="E217" t="n">
         <v>12.8</v>
@@ -5864,6 +7164,12 @@
       <c r="G217" t="n">
         <v>13.75</v>
       </c>
+      <c r="H217" t="n">
+        <v>0.8312615752220154</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0.2263181060552597</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5872,13 +7178,13 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.418269231</v>
+        <v>0.4182692307692307</v>
       </c>
       <c r="C218" t="n">
-        <v>0.072463768</v>
+        <v>0.07246376811594203</v>
       </c>
       <c r="D218" t="n">
-        <v>0.394230769</v>
+        <v>0.3942307692307692</v>
       </c>
       <c r="E218" t="n">
         <v>13.8</v>
@@ -5889,6 +7195,12 @@
       <c r="G218" t="n">
         <v>15.03</v>
       </c>
+      <c r="H218" t="n">
+        <v>0.8437447547912598</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0.2220214605331421</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5897,13 +7209,13 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.427157001</v>
+        <v>0.4271570014144271</v>
       </c>
       <c r="C219" t="n">
-        <v>0.08794326199999999</v>
+        <v>0.08794326241134752</v>
       </c>
       <c r="D219" t="n">
-        <v>0.396039604</v>
+        <v>0.396039603960396</v>
       </c>
       <c r="E219" t="n">
         <v>15.6</v>
@@ -5914,6 +7226,12 @@
       <c r="G219" t="n">
         <v>16.66</v>
       </c>
+      <c r="H219" t="n">
+        <v>0.8359268307685852</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0.2388498187065125</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5922,13 +7240,13 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.41980198</v>
+        <v>0.4198019801980198</v>
       </c>
       <c r="C220" t="n">
-        <v>0.083499006</v>
+        <v>0.08349900596421471</v>
       </c>
       <c r="D220" t="n">
-        <v>0.388118812</v>
+        <v>0.3881188118811882</v>
       </c>
       <c r="E220" t="n">
         <v>10.6</v>
@@ -5939,6 +7257,12 @@
       <c r="G220" t="n">
         <v>11.95</v>
       </c>
+      <c r="H220" t="n">
+        <v>0.8451264500617981</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0.2350154370069504</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5947,13 +7271,13 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.438356164</v>
+        <v>0.4383561643835616</v>
       </c>
       <c r="C221" t="n">
-        <v>0.090373281</v>
+        <v>0.09037328094302555</v>
       </c>
       <c r="D221" t="n">
-        <v>0.40704501</v>
+        <v>0.4070450097847358</v>
       </c>
       <c r="E221" t="n">
         <v>14.5</v>
@@ -5964,6 +7288,12 @@
       <c r="G221" t="n">
         <v>15.32</v>
       </c>
+      <c r="H221" t="n">
+        <v>0.8509616255760193</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0.2339233756065369</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5972,13 +7302,13 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.339100346</v>
+        <v>0.3391003460207613</v>
       </c>
       <c r="C222" t="n">
-        <v>0.097222222</v>
+        <v>0.09722222222222222</v>
       </c>
       <c r="D222" t="n">
-        <v>0.307958478</v>
+        <v>0.3079584775086505</v>
       </c>
       <c r="E222" t="n">
         <v>10.4</v>
@@ -5989,6 +7319,12 @@
       <c r="G222" t="n">
         <v>13.92</v>
       </c>
+      <c r="H222" t="n">
+        <v>0.8433425426483154</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0.2306958884000778</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5997,13 +7333,13 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.444924406</v>
+        <v>0.4449244060475162</v>
       </c>
       <c r="C223" t="n">
-        <v>0.125813449</v>
+        <v>0.1258134490238612</v>
       </c>
       <c r="D223" t="n">
-        <v>0.406047516</v>
+        <v>0.4060475161987041</v>
       </c>
       <c r="E223" t="n">
         <v>11.4</v>
@@ -6014,6 +7350,12 @@
       <c r="G223" t="n">
         <v>12.01</v>
       </c>
+      <c r="H223" t="n">
+        <v>0.8544140458106995</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0.2343422025442123</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6022,13 +7364,13 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.388443018</v>
+        <v>0.3884430176565007</v>
       </c>
       <c r="C224" t="n">
-        <v>0.08695652199999999</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="D224" t="n">
-        <v>0.359550562</v>
+        <v>0.3595505617977527</v>
       </c>
       <c r="E224" t="n">
         <v>15.4</v>
@@ -6039,6 +7381,12 @@
       <c r="G224" t="n">
         <v>13.12</v>
       </c>
+      <c r="H224" t="n">
+        <v>0.8353811502456665</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0.2238922268152237</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6047,13 +7395,13 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.423011844</v>
+        <v>0.4230118443316414</v>
       </c>
       <c r="C225" t="n">
-        <v>0.115449915</v>
+        <v>0.1154499151103565</v>
       </c>
       <c r="D225" t="n">
-        <v>0.385786802</v>
+        <v>0.3857868020304568</v>
       </c>
       <c r="E225" t="n">
         <v>14.1</v>
@@ -6064,6 +7412,12 @@
       <c r="G225" t="n">
         <v>13.05</v>
       </c>
+      <c r="H225" t="n">
+        <v>0.8323315382003784</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0.2469193786382675</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6072,13 +7426,13 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.327536232</v>
+        <v>0.3275362318840579</v>
       </c>
       <c r="C226" t="n">
-        <v>0.087209302</v>
+        <v>0.0872093023255814</v>
       </c>
       <c r="D226" t="n">
-        <v>0.298550725</v>
+        <v>0.2985507246376812</v>
       </c>
       <c r="E226" t="n">
         <v>13.2</v>
@@ -6089,6 +7443,12 @@
       <c r="G226" t="n">
         <v>13.58</v>
       </c>
+      <c r="H226" t="n">
+        <v>0.8227002024650574</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0.2328248620033264</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6097,13 +7457,13 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.417293233</v>
+        <v>0.4172932330827068</v>
       </c>
       <c r="C227" t="n">
-        <v>0.124528302</v>
+        <v>0.1245283018867925</v>
       </c>
       <c r="D227" t="n">
-        <v>0.390977444</v>
+        <v>0.3909774436090226</v>
       </c>
       <c r="E227" t="n">
         <v>16.4</v>
@@ -6114,6 +7474,12 @@
       <c r="G227" t="n">
         <v>16.71</v>
       </c>
+      <c r="H227" t="n">
+        <v>0.8549424409866333</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0.2423680573701859</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -6122,13 +7488,13 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.437137331</v>
+        <v>0.437137330754352</v>
       </c>
       <c r="C228" t="n">
-        <v>0.12038835</v>
+        <v>0.1203883495145631</v>
       </c>
       <c r="D228" t="n">
-        <v>0.410058027</v>
+        <v>0.4100580270793037</v>
       </c>
       <c r="E228" t="n">
         <v>13.8</v>
@@ -6139,6 +7505,12 @@
       <c r="G228" t="n">
         <v>13.64</v>
       </c>
+      <c r="H228" t="n">
+        <v>0.8450962901115417</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0.2197494655847549</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6147,13 +7519,13 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.309803922</v>
+        <v>0.3098039215686275</v>
       </c>
       <c r="C229" t="n">
-        <v>0.047244094</v>
+        <v>0.04724409448818898</v>
       </c>
       <c r="D229" t="n">
-        <v>0.294117647</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="E229" t="n">
         <v>13.1</v>
@@ -6164,6 +7536,12 @@
       <c r="G229" t="n">
         <v>14.33</v>
       </c>
+      <c r="H229" t="n">
+        <v>0.8336774706840515</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0.2248812615871429</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -6172,13 +7550,13 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.404181185</v>
+        <v>0.4041811846689896</v>
       </c>
       <c r="C230" t="n">
-        <v>0.09790209800000001</v>
+        <v>0.0979020979020979</v>
       </c>
       <c r="D230" t="n">
-        <v>0.383275261</v>
+        <v>0.3832752613240418</v>
       </c>
       <c r="E230" t="n">
         <v>12.8</v>
@@ -6189,6 +7567,12 @@
       <c r="G230" t="n">
         <v>12.88</v>
       </c>
+      <c r="H230" t="n">
+        <v>0.8511109352111816</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0.2610458433628082</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6197,13 +7581,13 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.47702407</v>
+        <v>0.4770240700218818</v>
       </c>
       <c r="C231" t="n">
-        <v>0.07912087900000001</v>
+        <v>0.07912087912087912</v>
       </c>
       <c r="D231" t="n">
-        <v>0.433260394</v>
+        <v>0.4332603938730853</v>
       </c>
       <c r="E231" t="n">
         <v>12</v>
@@ -6214,6 +7598,12 @@
       <c r="G231" t="n">
         <v>11.43</v>
       </c>
+      <c r="H231" t="n">
+        <v>0.8579846024513245</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0.2298489511013031</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -6222,13 +7612,13 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.370833333</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="C232" t="n">
-        <v>0.066945607</v>
+        <v>0.06694560669456066</v>
       </c>
       <c r="D232" t="n">
-        <v>0.341666667</v>
+        <v>0.3416666666666666</v>
       </c>
       <c r="E232" t="n">
         <v>14.2</v>
@@ -6239,6 +7629,12 @@
       <c r="G232" t="n">
         <v>15.32</v>
       </c>
+      <c r="H232" t="n">
+        <v>0.8503033518791199</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0.227794274687767</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6247,13 +7643,13 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.390852391</v>
+        <v>0.3908523908523909</v>
       </c>
       <c r="C233" t="n">
-        <v>0.11691023</v>
+        <v>0.116910229645094</v>
       </c>
       <c r="D233" t="n">
-        <v>0.37006237</v>
+        <v>0.3700623700623701</v>
       </c>
       <c r="E233" t="n">
         <v>13.1</v>
@@ -6264,6 +7660,12 @@
       <c r="G233" t="n">
         <v>16.71</v>
       </c>
+      <c r="H233" t="n">
+        <v>0.8459624648094177</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0.2433026134967804</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -6272,13 +7674,13 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.387323944</v>
+        <v>0.3873239436619719</v>
       </c>
       <c r="C234" t="n">
-        <v>0.07067137800000001</v>
+        <v>0.07067137809187279</v>
       </c>
       <c r="D234" t="n">
-        <v>0.362676056</v>
+        <v>0.3626760563380282</v>
       </c>
       <c r="E234" t="n">
         <v>14.1</v>
@@ -6289,6 +7691,12 @@
       <c r="G234" t="n">
         <v>15.78</v>
       </c>
+      <c r="H234" t="n">
+        <v>0.8419984579086304</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0.2526699006557465</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6297,13 +7705,13 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.394106814</v>
+        <v>0.3941068139963168</v>
       </c>
       <c r="C235" t="n">
-        <v>0.103512015</v>
+        <v>0.1035120147874307</v>
       </c>
       <c r="D235" t="n">
-        <v>0.360957643</v>
+        <v>0.3609576427255985</v>
       </c>
       <c r="E235" t="n">
         <v>13.3</v>
@@ -6314,6 +7722,12 @@
       <c r="G235" t="n">
         <v>15.37</v>
       </c>
+      <c r="H235" t="n">
+        <v>0.8393435478210449</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0.2328307032585144</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6322,10 +7736,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.389285714</v>
+        <v>0.3892857142857143</v>
       </c>
       <c r="C236" t="n">
-        <v>0.09677419399999999</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="D236" t="n">
         <v>0.375</v>
@@ -6339,6 +7753,12 @@
       <c r="G236" t="n">
         <v>12.82</v>
       </c>
+      <c r="H236" t="n">
+        <v>0.835845410823822</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0.2425568699836731</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6350,7 +7770,7 @@
         <v>0.444</v>
       </c>
       <c r="C237" t="n">
-        <v>0.07228915700000001</v>
+        <v>0.07228915662650601</v>
       </c>
       <c r="D237" t="n">
         <v>0.396</v>
@@ -6364,6 +7784,12 @@
       <c r="G237" t="n">
         <v>15.96</v>
       </c>
+      <c r="H237" t="n">
+        <v>0.8420668840408325</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0.2339037358760834</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -6372,13 +7798,13 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.408695652</v>
+        <v>0.4086956521739131</v>
       </c>
       <c r="C238" t="n">
-        <v>0.113372093</v>
+        <v>0.1133720930232558</v>
       </c>
       <c r="D238" t="n">
-        <v>0.373913043</v>
+        <v>0.3739130434782608</v>
       </c>
       <c r="E238" t="n">
         <v>15.9</v>
@@ -6389,6 +7815,12 @@
       <c r="G238" t="n">
         <v>15.73</v>
       </c>
+      <c r="H238" t="n">
+        <v>0.8343755602836609</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0.2301212102174759</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -6397,13 +7829,13 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.39941691</v>
+        <v>0.3994169096209913</v>
       </c>
       <c r="C239" t="n">
-        <v>0.102339181</v>
+        <v>0.1023391812865497</v>
       </c>
       <c r="D239" t="n">
-        <v>0.38483965</v>
+        <v>0.3848396501457725</v>
       </c>
       <c r="E239" t="n">
         <v>14.4</v>
@@ -6414,6 +7846,12 @@
       <c r="G239" t="n">
         <v>13.41</v>
       </c>
+      <c r="H239" t="n">
+        <v>0.8387821316719055</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0.2263683825731277</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -6422,13 +7860,13 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.380952381</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="C240" t="n">
-        <v>0.08059701499999999</v>
+        <v>0.08059701492537313</v>
       </c>
       <c r="D240" t="n">
-        <v>0.366071429</v>
+        <v>0.3660714285714286</v>
       </c>
       <c r="E240" t="n">
         <v>12.3</v>
@@ -6439,6 +7877,12 @@
       <c r="G240" t="n">
         <v>13.05</v>
       </c>
+      <c r="H240" t="n">
+        <v>0.8396927714347839</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0.2828195095062256</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -6447,13 +7891,13 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.412645591</v>
+        <v>0.4126455906821963</v>
       </c>
       <c r="C241" t="n">
-        <v>0.110183639</v>
+        <v>0.1101836393989983</v>
       </c>
       <c r="D241" t="n">
-        <v>0.366056572</v>
+        <v>0.3660565723793677</v>
       </c>
       <c r="E241" t="n">
         <v>14</v>
@@ -6464,6 +7908,12 @@
       <c r="G241" t="n">
         <v>13.75</v>
       </c>
+      <c r="H241" t="n">
+        <v>0.8420699238777161</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0.235561192035675</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6472,13 +7922,13 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.557894737</v>
+        <v>0.5578947368421052</v>
       </c>
       <c r="C242" t="n">
-        <v>0.144366197</v>
+        <v>0.1443661971830986</v>
       </c>
       <c r="D242" t="n">
-        <v>0.533333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E242" t="n">
         <v>14.6</v>
@@ -6489,6 +7939,12 @@
       <c r="G242" t="n">
         <v>16.65</v>
       </c>
+      <c r="H242" t="n">
+        <v>0.8623017072677612</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0.2369515299797058</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6524,6 +7980,16 @@
       <c r="G243" t="inlineStr">
         <is>
           <t>14.787 ± 1.681</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>0.844 ± 0.010</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>0.238 ± 0.014</t>
         </is>
       </c>
     </row>
